--- a/source/connector_service.xlsx
+++ b/source/connector_service.xlsx
@@ -8,13 +8,16 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\enterprise\omega\Папки отделов\Департамент закупівель та логістики\Відділ реінжинірингу процесів закупівель\Master data\З'єднувач\обработка\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EE685C71-D5F2-4526-8F10-3A83FA5DCE16}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{42C4A13E-3789-457F-B1D2-A11F3EB39553}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="11625" xr2:uid="{CE2CFF51-9F38-4EC7-9E81-657A284ABED4}"/>
   </bookViews>
   <sheets>
     <sheet name="Аркуш1" sheetId="1" r:id="rId1"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Аркуш1!$A$1:$AJ$61</definedName>
+  </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -25,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="985" uniqueCount="282">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1021" uniqueCount="286">
   <si>
     <t>Номер карточки</t>
   </si>
@@ -1393,6 +1396,18 @@
   </si>
   <si>
     <t>_315019031</t>
+  </si>
+  <si>
+    <t>_6900240990</t>
+  </si>
+  <si>
+    <t>_02.210.7150.080</t>
+  </si>
+  <si>
+    <t>_32351192793</t>
+  </si>
+  <si>
+    <t>_DK-11.3513110</t>
   </si>
 </sst>
 </file>
@@ -1779,7 +1794,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A3118E0D-448D-4EEB-9348-1247B3113B2C}">
-  <dimension ref="A1:AJ59"/>
+  <dimension ref="A1:AJ61"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="23" customWidth="1"/>
@@ -2733,26 +2748,24 @@
     </row>
     <row r="13" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
-        <v>66</v>
+        <v>284</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>67</v>
+        <v>285</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>68</v>
+        <v>32</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="E13" s="2" t="s">
-        <v>69</v>
-      </c>
+        <v>32</v>
+      </c>
+      <c r="E13" s="2"/>
       <c r="F13" s="2"/>
       <c r="G13" s="2" t="s">
-        <v>70</v>
+        <v>34</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>71</v>
+        <v>35</v>
       </c>
       <c r="I13" s="2" t="s">
         <v>36</v>
@@ -2760,8 +2773,12 @@
       <c r="J13" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="K13" s="2"/>
-      <c r="L13" s="2"/>
+      <c r="K13" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="L13" s="2" t="s">
+        <v>39</v>
+      </c>
       <c r="M13" s="2" t="s">
         <v>40</v>
       </c>
@@ -2783,21 +2800,11 @@
       <c r="S13" s="2">
         <v>1.5</v>
       </c>
-      <c r="T13" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="U13" s="2" t="s">
-        <v>73</v>
-      </c>
-      <c r="V13" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="W13" s="2" t="s">
-        <v>74</v>
-      </c>
-      <c r="X13" s="2" t="s">
-        <v>75</v>
-      </c>
+      <c r="T13" s="2"/>
+      <c r="U13" s="2"/>
+      <c r="V13" s="2"/>
+      <c r="W13" s="2"/>
+      <c r="X13" s="2"/>
       <c r="Y13" s="2"/>
       <c r="Z13" s="2"/>
       <c r="AA13" s="2"/>
@@ -2810,24 +2817,24 @@
       <c r="AH13" s="2"/>
       <c r="AI13" s="2"/>
       <c r="AJ13">
-        <v>130</v>
+        <v>129</v>
       </c>
     </row>
     <row r="14" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
-        <v>76</v>
+        <v>66</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>77</v>
+        <v>67</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>78</v>
+        <v>68</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>78</v>
+        <v>68</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>79</v>
+        <v>69</v>
       </c>
       <c r="F14" s="2"/>
       <c r="G14" s="2" t="s">
@@ -2848,10 +2855,10 @@
         <v>40</v>
       </c>
       <c r="N14" s="2" t="s">
-        <v>80</v>
+        <v>41</v>
       </c>
       <c r="O14" s="2" t="s">
-        <v>80</v>
+        <v>41</v>
       </c>
       <c r="P14" s="2" t="s">
         <v>42</v>
@@ -2860,7 +2867,7 @@
         <v>43</v>
       </c>
       <c r="R14" s="2" t="s">
-        <v>81</v>
+        <v>44</v>
       </c>
       <c r="S14" s="2">
         <v>1.5</v>
@@ -2897,23 +2904,21 @@
     </row>
     <row r="15" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>83</v>
+        <v>77</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>84</v>
+        <v>78</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>84</v>
+        <v>78</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>85</v>
-      </c>
-      <c r="F15" s="2" t="s">
-        <v>86</v>
-      </c>
+        <v>79</v>
+      </c>
+      <c r="F15" s="2"/>
       <c r="G15" s="2" t="s">
         <v>70</v>
       </c>
@@ -2923,17 +2928,19 @@
       <c r="I15" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="J15" s="2"/>
+      <c r="J15" s="2" t="s">
+        <v>37</v>
+      </c>
       <c r="K15" s="2"/>
       <c r="L15" s="2"/>
       <c r="M15" s="2" t="s">
         <v>40</v>
       </c>
       <c r="N15" s="2" t="s">
-        <v>41</v>
+        <v>80</v>
       </c>
       <c r="O15" s="2" t="s">
-        <v>41</v>
+        <v>80</v>
       </c>
       <c r="P15" s="2" t="s">
         <v>42</v>
@@ -2942,7 +2949,7 @@
         <v>43</v>
       </c>
       <c r="R15" s="2" t="s">
-        <v>44</v>
+        <v>81</v>
       </c>
       <c r="S15" s="2">
         <v>1.5</v>
@@ -2959,7 +2966,9 @@
       <c r="W15" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="X15" s="2"/>
+      <c r="X15" s="2" t="s">
+        <v>75</v>
+      </c>
       <c r="Y15" s="2"/>
       <c r="Z15" s="2"/>
       <c r="AA15" s="2"/>
@@ -2977,19 +2986,19 @@
     </row>
     <row r="16" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
-        <v>87</v>
+        <v>82</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>88</v>
+        <v>83</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>89</v>
+        <v>84</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>89</v>
+        <v>84</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="F16" s="2" t="s">
         <v>86</v>
@@ -3010,10 +3019,10 @@
         <v>40</v>
       </c>
       <c r="N16" s="2" t="s">
-        <v>80</v>
+        <v>41</v>
       </c>
       <c r="O16" s="2" t="s">
-        <v>80</v>
+        <v>41</v>
       </c>
       <c r="P16" s="2" t="s">
         <v>42</v>
@@ -3022,7 +3031,7 @@
         <v>43</v>
       </c>
       <c r="R16" s="2" t="s">
-        <v>81</v>
+        <v>44</v>
       </c>
       <c r="S16" s="2">
         <v>1.5</v>
@@ -3057,19 +3066,19 @@
     </row>
     <row r="17" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="F17" s="2" t="s">
         <v>86</v>
@@ -3119,9 +3128,7 @@
       <c r="W17" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="X17" s="2" t="s">
-        <v>75</v>
-      </c>
+      <c r="X17" s="2"/>
       <c r="Y17" s="2"/>
       <c r="Z17" s="2"/>
       <c r="AA17" s="2"/>
@@ -3139,19 +3146,19 @@
     </row>
     <row r="18" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>97</v>
+        <v>93</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>97</v>
+        <v>93</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="F18" s="2" t="s">
         <v>86</v>
@@ -3172,10 +3179,10 @@
         <v>40</v>
       </c>
       <c r="N18" s="2" t="s">
-        <v>41</v>
+        <v>80</v>
       </c>
       <c r="O18" s="2" t="s">
-        <v>41</v>
+        <v>80</v>
       </c>
       <c r="P18" s="2" t="s">
         <v>42</v>
@@ -3184,7 +3191,7 @@
         <v>43</v>
       </c>
       <c r="R18" s="2" t="s">
-        <v>44</v>
+        <v>81</v>
       </c>
       <c r="S18" s="2">
         <v>1.5</v>
@@ -3221,21 +3228,23 @@
     </row>
     <row r="19" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
-        <v>99</v>
+        <v>282</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>100</v>
+        <v>283</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>68</v>
+        <v>93</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>68</v>
+        <v>93</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="F19" s="2"/>
+        <v>94</v>
+      </c>
+      <c r="F19" s="2" t="s">
+        <v>86</v>
+      </c>
       <c r="G19" s="2" t="s">
         <v>70</v>
       </c>
@@ -3245,19 +3254,17 @@
       <c r="I19" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="J19" s="2" t="s">
-        <v>37</v>
-      </c>
+      <c r="J19" s="2"/>
       <c r="K19" s="2"/>
       <c r="L19" s="2"/>
       <c r="M19" s="2" t="s">
         <v>40</v>
       </c>
       <c r="N19" s="2" t="s">
-        <v>41</v>
+        <v>80</v>
       </c>
       <c r="O19" s="2" t="s">
-        <v>41</v>
+        <v>80</v>
       </c>
       <c r="P19" s="2" t="s">
         <v>42</v>
@@ -3266,7 +3273,7 @@
         <v>43</v>
       </c>
       <c r="R19" s="2" t="s">
-        <v>44</v>
+        <v>81</v>
       </c>
       <c r="S19" s="2">
         <v>1.5</v>
@@ -3303,21 +3310,23 @@
     </row>
     <row r="20" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
-        <v>101</v>
+        <v>95</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>102</v>
+        <v>96</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>68</v>
+        <v>97</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>68</v>
+        <v>97</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="F20" s="2"/>
+        <v>98</v>
+      </c>
+      <c r="F20" s="2" t="s">
+        <v>86</v>
+      </c>
       <c r="G20" s="2" t="s">
         <v>70</v>
       </c>
@@ -3327,9 +3336,7 @@
       <c r="I20" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="J20" s="2" t="s">
-        <v>37</v>
-      </c>
+      <c r="J20" s="2"/>
       <c r="K20" s="2"/>
       <c r="L20" s="2"/>
       <c r="M20" s="2" t="s">
@@ -3385,26 +3392,26 @@
     </row>
     <row r="21" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>105</v>
+        <v>68</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>105</v>
+        <v>68</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>106</v>
+        <v>69</v>
       </c>
       <c r="F21" s="2"/>
       <c r="G21" s="2" t="s">
-        <v>107</v>
+        <v>70</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>108</v>
+        <v>71</v>
       </c>
       <c r="I21" s="2" t="s">
         <v>36</v>
@@ -3415,70 +3422,78 @@
       <c r="K21" s="2"/>
       <c r="L21" s="2"/>
       <c r="M21" s="2" t="s">
-        <v>109</v>
+        <v>40</v>
       </c>
       <c r="N21" s="2" t="s">
-        <v>110</v>
-      </c>
-      <c r="O21" s="2"/>
-      <c r="P21" s="2"/>
-      <c r="Q21" s="2"/>
-      <c r="R21" s="2"/>
-      <c r="S21" s="2"/>
-      <c r="T21" s="2"/>
-      <c r="U21" s="2"/>
-      <c r="V21" s="2"/>
-      <c r="W21" s="2"/>
-      <c r="X21" s="2"/>
-      <c r="Y21" s="2" t="s">
-        <v>111</v>
-      </c>
-      <c r="Z21" s="2" t="s">
-        <v>112</v>
-      </c>
-      <c r="AA21" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="AB21" s="2">
-        <v>6</v>
-      </c>
-      <c r="AC21" s="2" t="s">
-        <v>113</v>
-      </c>
-      <c r="AD21" s="2" t="s">
-        <v>114</v>
-      </c>
+        <v>41</v>
+      </c>
+      <c r="O21" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="P21" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="Q21" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="R21" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="S21" s="2">
+        <v>1.5</v>
+      </c>
+      <c r="T21" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="U21" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="V21" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="W21" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="X21" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="Y21" s="2"/>
+      <c r="Z21" s="2"/>
+      <c r="AA21" s="2"/>
+      <c r="AB21" s="2"/>
+      <c r="AC21" s="2"/>
+      <c r="AD21" s="2"/>
       <c r="AE21" s="2"/>
       <c r="AF21" s="2"/>
       <c r="AG21" s="2"/>
       <c r="AH21" s="2"/>
       <c r="AI21" s="2"/>
       <c r="AJ21">
-        <v>75</v>
+        <v>130</v>
       </c>
     </row>
     <row r="22" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
-        <v>115</v>
+        <v>101</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>116</v>
+        <v>102</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>117</v>
+        <v>68</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>117</v>
+        <v>68</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>118</v>
+        <v>69</v>
       </c>
       <c r="F22" s="2"/>
       <c r="G22" s="2" t="s">
-        <v>107</v>
+        <v>70</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>108</v>
+        <v>71</v>
       </c>
       <c r="I22" s="2" t="s">
         <v>36</v>
@@ -3489,63 +3504,71 @@
       <c r="K22" s="2"/>
       <c r="L22" s="2"/>
       <c r="M22" s="2" t="s">
-        <v>109</v>
+        <v>40</v>
       </c>
       <c r="N22" s="2" t="s">
-        <v>119</v>
-      </c>
-      <c r="O22" s="2"/>
-      <c r="P22" s="2"/>
-      <c r="Q22" s="2"/>
-      <c r="R22" s="2"/>
-      <c r="S22" s="2"/>
-      <c r="T22" s="2"/>
-      <c r="U22" s="2"/>
-      <c r="V22" s="2"/>
-      <c r="W22" s="2"/>
-      <c r="X22" s="2"/>
-      <c r="Y22" s="2" t="s">
-        <v>111</v>
-      </c>
-      <c r="Z22" s="2" t="s">
-        <v>112</v>
-      </c>
-      <c r="AA22" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="AB22" s="2">
-        <v>8</v>
-      </c>
-      <c r="AC22" s="2" t="s">
-        <v>113</v>
-      </c>
-      <c r="AD22" s="2" t="s">
-        <v>114</v>
-      </c>
+        <v>41</v>
+      </c>
+      <c r="O22" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="P22" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="Q22" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="R22" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="S22" s="2">
+        <v>1.5</v>
+      </c>
+      <c r="T22" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="U22" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="V22" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="W22" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="X22" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="Y22" s="2"/>
+      <c r="Z22" s="2"/>
+      <c r="AA22" s="2"/>
+      <c r="AB22" s="2"/>
+      <c r="AC22" s="2"/>
+      <c r="AD22" s="2"/>
       <c r="AE22" s="2"/>
       <c r="AF22" s="2"/>
       <c r="AG22" s="2"/>
       <c r="AH22" s="2"/>
       <c r="AI22" s="2"/>
       <c r="AJ22">
-        <v>75</v>
+        <v>130</v>
       </c>
     </row>
     <row r="23" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
-        <v>120</v>
+        <v>103</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>121</v>
+        <v>104</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>117</v>
+        <v>105</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>117</v>
+        <v>105</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>118</v>
+        <v>106</v>
       </c>
       <c r="F23" s="2"/>
       <c r="G23" s="2" t="s">
@@ -3566,7 +3589,7 @@
         <v>109</v>
       </c>
       <c r="N23" s="2" t="s">
-        <v>119</v>
+        <v>110</v>
       </c>
       <c r="O23" s="2"/>
       <c r="P23" s="2"/>
@@ -3588,7 +3611,7 @@
         <v>55</v>
       </c>
       <c r="AB23" s="2">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="AC23" s="2" t="s">
         <v>113</v>
@@ -3607,19 +3630,19 @@
     </row>
     <row r="24" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="s">
-        <v>122</v>
+        <v>115</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>123</v>
+        <v>116</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>124</v>
+        <v>117</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>124</v>
+        <v>117</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>125</v>
+        <v>118</v>
       </c>
       <c r="F24" s="2"/>
       <c r="G24" s="2" t="s">
@@ -3632,7 +3655,7 @@
         <v>36</v>
       </c>
       <c r="J24" s="2" t="s">
-        <v>55</v>
+        <v>37</v>
       </c>
       <c r="K24" s="2"/>
       <c r="L24" s="2"/>
@@ -3640,7 +3663,7 @@
         <v>109</v>
       </c>
       <c r="N24" s="2" t="s">
-        <v>110</v>
+        <v>119</v>
       </c>
       <c r="O24" s="2"/>
       <c r="P24" s="2"/>
@@ -3662,7 +3685,7 @@
         <v>55</v>
       </c>
       <c r="AB24" s="2">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AC24" s="2" t="s">
         <v>113</v>
@@ -3676,24 +3699,24 @@
       <c r="AH24" s="2"/>
       <c r="AI24" s="2"/>
       <c r="AJ24">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="25" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A25" s="2" t="s">
-        <v>126</v>
+        <v>120</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>127</v>
+        <v>121</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>128</v>
+        <v>117</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>128</v>
+        <v>117</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>129</v>
+        <v>118</v>
       </c>
       <c r="F25" s="2"/>
       <c r="G25" s="2" t="s">
@@ -3706,7 +3729,7 @@
         <v>36</v>
       </c>
       <c r="J25" s="2" t="s">
-        <v>55</v>
+        <v>37</v>
       </c>
       <c r="K25" s="2"/>
       <c r="L25" s="2"/>
@@ -3750,15 +3773,15 @@
       <c r="AH25" s="2"/>
       <c r="AI25" s="2"/>
       <c r="AJ25">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="26" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A26" s="2" t="s">
-        <v>130</v>
+        <v>122</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>131</v>
+        <v>123</v>
       </c>
       <c r="C26" s="2" t="s">
         <v>124</v>
@@ -3829,19 +3852,19 @@
     </row>
     <row r="27" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A27" s="2" t="s">
-        <v>132</v>
+        <v>126</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>133</v>
+        <v>127</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>260</v>
+        <v>128</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>260</v>
+        <v>128</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>261</v>
+        <v>129</v>
       </c>
       <c r="F27" s="2"/>
       <c r="G27" s="2" t="s">
@@ -3854,7 +3877,7 @@
         <v>36</v>
       </c>
       <c r="J27" s="2" t="s">
-        <v>134</v>
+        <v>55</v>
       </c>
       <c r="K27" s="2"/>
       <c r="L27" s="2"/>
@@ -3862,7 +3885,7 @@
         <v>109</v>
       </c>
       <c r="N27" s="2" t="s">
-        <v>110</v>
+        <v>119</v>
       </c>
       <c r="O27" s="2"/>
       <c r="P27" s="2"/>
@@ -3875,7 +3898,7 @@
       <c r="W27" s="2"/>
       <c r="X27" s="2"/>
       <c r="Y27" s="2" t="s">
-        <v>211</v>
+        <v>111</v>
       </c>
       <c r="Z27" s="2" t="s">
         <v>112</v>
@@ -3884,7 +3907,7 @@
         <v>55</v>
       </c>
       <c r="AB27" s="2">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AC27" s="2" t="s">
         <v>113</v>
@@ -3898,24 +3921,24 @@
       <c r="AH27" s="2"/>
       <c r="AI27" s="2"/>
       <c r="AJ27">
-        <v>77</v>
+        <v>76</v>
       </c>
     </row>
     <row r="28" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A28" s="2" t="s">
-        <v>135</v>
+        <v>130</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>136</v>
+        <v>131</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>262</v>
+        <v>124</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>262</v>
+        <v>124</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>263</v>
+        <v>125</v>
       </c>
       <c r="F28" s="2"/>
       <c r="G28" s="2" t="s">
@@ -3928,7 +3951,7 @@
         <v>36</v>
       </c>
       <c r="J28" s="2" t="s">
-        <v>134</v>
+        <v>55</v>
       </c>
       <c r="K28" s="2"/>
       <c r="L28" s="2"/>
@@ -3936,7 +3959,7 @@
         <v>109</v>
       </c>
       <c r="N28" s="2" t="s">
-        <v>119</v>
+        <v>110</v>
       </c>
       <c r="O28" s="2"/>
       <c r="P28" s="2"/>
@@ -3949,7 +3972,7 @@
       <c r="W28" s="2"/>
       <c r="X28" s="2"/>
       <c r="Y28" s="2" t="s">
-        <v>211</v>
+        <v>111</v>
       </c>
       <c r="Z28" s="2" t="s">
         <v>112</v>
@@ -3958,7 +3981,7 @@
         <v>55</v>
       </c>
       <c r="AB28" s="2">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="AC28" s="2" t="s">
         <v>113</v>
@@ -3972,24 +3995,24 @@
       <c r="AH28" s="2"/>
       <c r="AI28" s="2"/>
       <c r="AJ28">
-        <v>77</v>
+        <v>76</v>
       </c>
     </row>
     <row r="29" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A29" s="2" t="s">
-        <v>137</v>
+        <v>132</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>138</v>
+        <v>133</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>264</v>
+        <v>260</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>264</v>
+        <v>260</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>265</v>
+        <v>261</v>
       </c>
       <c r="F29" s="2"/>
       <c r="G29" s="2" t="s">
@@ -4029,7 +4052,7 @@
         <v>112</v>
       </c>
       <c r="AA29" s="2" t="s">
-        <v>139</v>
+        <v>55</v>
       </c>
       <c r="AB29" s="2">
         <v>6</v>
@@ -4046,30 +4069,46 @@
       <c r="AH29" s="2"/>
       <c r="AI29" s="2"/>
       <c r="AJ29">
-        <v>78</v>
+        <v>77</v>
       </c>
     </row>
     <row r="30" spans="1:36" x14ac:dyDescent="0.25">
-      <c r="A30" t="s">
-        <v>268</v>
-      </c>
-      <c r="B30" t="s">
-        <v>269</v>
-      </c>
-      <c r="C30" t="s">
-        <v>276</v>
-      </c>
-      <c r="D30" s="2"/>
-      <c r="E30" s="2"/>
+      <c r="A30" s="2" t="s">
+        <v>135</v>
+      </c>
+      <c r="B30" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="C30" s="2" t="s">
+        <v>262</v>
+      </c>
+      <c r="D30" s="2" t="s">
+        <v>262</v>
+      </c>
+      <c r="E30" s="2" t="s">
+        <v>263</v>
+      </c>
       <c r="F30" s="2"/>
-      <c r="G30" s="2"/>
-      <c r="H30" s="2"/>
-      <c r="I30" s="2"/>
-      <c r="J30" s="2"/>
+      <c r="G30" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="H30" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="I30" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="J30" s="2" t="s">
+        <v>134</v>
+      </c>
       <c r="K30" s="2"/>
       <c r="L30" s="2"/>
-      <c r="M30" s="2"/>
-      <c r="N30" s="2"/>
+      <c r="M30" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="N30" s="2" t="s">
+        <v>119</v>
+      </c>
       <c r="O30" s="2"/>
       <c r="P30" s="2"/>
       <c r="Q30" s="2"/>
@@ -4080,42 +4119,70 @@
       <c r="V30" s="2"/>
       <c r="W30" s="2"/>
       <c r="X30" s="2"/>
-      <c r="Y30" s="2"/>
-      <c r="Z30" s="2"/>
-      <c r="AA30" s="2"/>
-      <c r="AB30" s="2"/>
-      <c r="AC30" s="2"/>
-      <c r="AD30" s="2"/>
+      <c r="Y30" s="2" t="s">
+        <v>211</v>
+      </c>
+      <c r="Z30" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="AA30" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="AB30" s="2">
+        <v>8</v>
+      </c>
+      <c r="AC30" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="AD30" s="2" t="s">
+        <v>114</v>
+      </c>
       <c r="AE30" s="2"/>
       <c r="AF30" s="2"/>
       <c r="AG30" s="2"/>
       <c r="AH30" s="2"/>
       <c r="AI30" s="2"/>
       <c r="AJ30">
-        <v>74</v>
+        <v>77</v>
       </c>
     </row>
     <row r="31" spans="1:36" x14ac:dyDescent="0.25">
-      <c r="A31" t="s">
-        <v>270</v>
-      </c>
-      <c r="B31" t="s">
-        <v>271</v>
-      </c>
-      <c r="C31" t="s">
-        <v>277</v>
-      </c>
-      <c r="D31" s="2"/>
-      <c r="E31" s="2"/>
+      <c r="A31" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="B31" s="2" t="s">
+        <v>138</v>
+      </c>
+      <c r="C31" s="2" t="s">
+        <v>264</v>
+      </c>
+      <c r="D31" s="2" t="s">
+        <v>264</v>
+      </c>
+      <c r="E31" s="2" t="s">
+        <v>265</v>
+      </c>
       <c r="F31" s="2"/>
-      <c r="G31" s="2"/>
-      <c r="H31" s="2"/>
-      <c r="I31" s="2"/>
-      <c r="J31" s="2"/>
+      <c r="G31" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="H31" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="I31" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="J31" s="2" t="s">
+        <v>134</v>
+      </c>
       <c r="K31" s="2"/>
       <c r="L31" s="2"/>
-      <c r="M31" s="2"/>
-      <c r="N31" s="2"/>
+      <c r="M31" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="N31" s="2" t="s">
+        <v>110</v>
+      </c>
       <c r="O31" s="2"/>
       <c r="P31" s="2"/>
       <c r="Q31" s="2"/>
@@ -4126,30 +4193,42 @@
       <c r="V31" s="2"/>
       <c r="W31" s="2"/>
       <c r="X31" s="2"/>
-      <c r="Y31" s="2"/>
-      <c r="Z31" s="2"/>
-      <c r="AA31" s="2"/>
-      <c r="AB31" s="2"/>
-      <c r="AC31" s="2"/>
-      <c r="AD31" s="2"/>
+      <c r="Y31" s="2" t="s">
+        <v>211</v>
+      </c>
+      <c r="Z31" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="AA31" s="2" t="s">
+        <v>139</v>
+      </c>
+      <c r="AB31" s="2">
+        <v>6</v>
+      </c>
+      <c r="AC31" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="AD31" s="2" t="s">
+        <v>114</v>
+      </c>
       <c r="AE31" s="2"/>
       <c r="AF31" s="2"/>
       <c r="AG31" s="2"/>
       <c r="AH31" s="2"/>
       <c r="AI31" s="2"/>
       <c r="AJ31">
-        <v>74</v>
+        <v>78</v>
       </c>
     </row>
     <row r="32" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>272</v>
+        <v>268</v>
       </c>
       <c r="B32" t="s">
-        <v>273</v>
+        <v>269</v>
       </c>
       <c r="C32" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="D32" s="2"/>
       <c r="E32" s="2"/>
@@ -4189,13 +4268,13 @@
     </row>
     <row r="33" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>274</v>
+        <v>270</v>
       </c>
       <c r="B33" t="s">
-        <v>275</v>
+        <v>271</v>
       </c>
       <c r="C33" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="D33" s="2"/>
       <c r="E33" s="2"/>
@@ -4234,42 +4313,26 @@
       </c>
     </row>
     <row r="34" spans="1:36" x14ac:dyDescent="0.25">
-      <c r="A34" s="2" t="s">
-        <v>140</v>
-      </c>
-      <c r="B34" s="2" t="s">
-        <v>141</v>
-      </c>
-      <c r="C34" s="2" t="s">
-        <v>266</v>
-      </c>
-      <c r="D34" s="2" t="s">
-        <v>266</v>
-      </c>
-      <c r="E34" s="2" t="s">
-        <v>267</v>
-      </c>
+      <c r="A34" t="s">
+        <v>272</v>
+      </c>
+      <c r="B34" t="s">
+        <v>273</v>
+      </c>
+      <c r="C34" t="s">
+        <v>278</v>
+      </c>
+      <c r="D34" s="2"/>
+      <c r="E34" s="2"/>
       <c r="F34" s="2"/>
-      <c r="G34" s="2" t="s">
-        <v>107</v>
-      </c>
-      <c r="H34" s="2" t="s">
-        <v>108</v>
-      </c>
-      <c r="I34" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="J34" s="2" t="s">
-        <v>134</v>
-      </c>
+      <c r="G34" s="2"/>
+      <c r="H34" s="2"/>
+      <c r="I34" s="2"/>
+      <c r="J34" s="2"/>
       <c r="K34" s="2"/>
       <c r="L34" s="2"/>
-      <c r="M34" s="2" t="s">
-        <v>109</v>
-      </c>
-      <c r="N34" s="2" t="s">
-        <v>119</v>
-      </c>
+      <c r="M34" s="2"/>
+      <c r="N34" s="2"/>
       <c r="O34" s="2"/>
       <c r="P34" s="2"/>
       <c r="Q34" s="2"/>
@@ -4280,204 +4343,156 @@
       <c r="V34" s="2"/>
       <c r="W34" s="2"/>
       <c r="X34" s="2"/>
-      <c r="Y34" s="2" t="s">
-        <v>211</v>
-      </c>
-      <c r="Z34" s="2" t="s">
-        <v>112</v>
-      </c>
-      <c r="AA34" s="2" t="s">
-        <v>139</v>
-      </c>
-      <c r="AB34" s="2">
-        <v>8</v>
-      </c>
-      <c r="AC34" s="2" t="s">
-        <v>113</v>
-      </c>
-      <c r="AD34" s="2" t="s">
-        <v>114</v>
-      </c>
+      <c r="Y34" s="2"/>
+      <c r="Z34" s="2"/>
+      <c r="AA34" s="2"/>
+      <c r="AB34" s="2"/>
+      <c r="AC34" s="2"/>
+      <c r="AD34" s="2"/>
       <c r="AE34" s="2"/>
       <c r="AF34" s="2"/>
       <c r="AG34" s="2"/>
       <c r="AH34" s="2"/>
       <c r="AI34" s="2"/>
       <c r="AJ34">
-        <v>78</v>
+        <v>74</v>
       </c>
     </row>
-    <row r="35" spans="1:36" s="4" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A35" s="2" t="s">
-        <v>143</v>
-      </c>
-      <c r="B35" s="2" t="s">
-        <v>144</v>
-      </c>
-      <c r="C35" s="2" t="s">
-        <v>145</v>
-      </c>
-      <c r="D35" s="2" t="s">
-        <v>145</v>
-      </c>
-      <c r="E35" s="2" t="s">
-        <v>146</v>
-      </c>
+    <row r="35" spans="1:36" x14ac:dyDescent="0.25">
+      <c r="A35" t="s">
+        <v>274</v>
+      </c>
+      <c r="B35" t="s">
+        <v>275</v>
+      </c>
+      <c r="C35" t="s">
+        <v>279</v>
+      </c>
+      <c r="D35" s="2"/>
+      <c r="E35" s="2"/>
       <c r="F35" s="2"/>
-      <c r="G35" s="2" t="s">
-        <v>147</v>
-      </c>
-      <c r="H35" s="2" t="s">
-        <v>148</v>
-      </c>
-      <c r="I35" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="J35" s="2" t="s">
-        <v>55</v>
-      </c>
+      <c r="G35" s="2"/>
+      <c r="H35" s="2"/>
+      <c r="I35" s="2"/>
+      <c r="J35" s="2"/>
       <c r="K35" s="2"/>
       <c r="L35" s="2"/>
-      <c r="M35" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="N35" s="2" t="s">
-        <v>149</v>
-      </c>
-      <c r="O35" s="2" t="s">
-        <v>149</v>
-      </c>
-      <c r="P35" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="Q35" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="R35" s="2" t="s">
-        <v>150</v>
-      </c>
-      <c r="S35" s="2">
-        <v>1</v>
-      </c>
+      <c r="M35" s="2"/>
+      <c r="N35" s="2"/>
+      <c r="O35" s="2"/>
+      <c r="P35" s="2"/>
+      <c r="Q35" s="2"/>
+      <c r="R35" s="2"/>
+      <c r="S35" s="2"/>
       <c r="T35" s="2"/>
       <c r="U35" s="2"/>
       <c r="V35" s="2"/>
       <c r="W35" s="2"/>
       <c r="X35" s="2"/>
-      <c r="Y35" s="2" t="s">
-        <v>111</v>
-      </c>
+      <c r="Y35" s="2"/>
       <c r="Z35" s="2"/>
       <c r="AA35" s="2"/>
       <c r="AB35" s="2"/>
       <c r="AC35" s="2"/>
       <c r="AD35" s="2"/>
-      <c r="AE35" s="2" t="s">
-        <v>151</v>
-      </c>
-      <c r="AF35" s="2" t="s">
-        <v>152</v>
-      </c>
+      <c r="AE35" s="2"/>
+      <c r="AF35" s="2"/>
       <c r="AG35" s="2"/>
       <c r="AH35" s="2"/>
       <c r="AI35" s="2"/>
-      <c r="AJ35" s="4">
-        <v>183</v>
+      <c r="AJ35">
+        <v>74</v>
       </c>
     </row>
-    <row r="36" spans="1:36" s="4" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A36" s="2" t="s">
-        <v>153</v>
+        <v>140</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>154</v>
+        <v>141</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>155</v>
+        <v>266</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>155</v>
+        <v>266</v>
       </c>
       <c r="E36" s="2" t="s">
-        <v>156</v>
+        <v>267</v>
       </c>
       <c r="F36" s="2"/>
       <c r="G36" s="2" t="s">
-        <v>147</v>
+        <v>107</v>
       </c>
       <c r="H36" s="2" t="s">
-        <v>148</v>
+        <v>108</v>
       </c>
       <c r="I36" s="2" t="s">
         <v>36</v>
       </c>
       <c r="J36" s="2" t="s">
-        <v>55</v>
+        <v>134</v>
       </c>
       <c r="K36" s="2"/>
       <c r="L36" s="2"/>
       <c r="M36" s="2" t="s">
-        <v>40</v>
+        <v>109</v>
       </c>
       <c r="N36" s="2" t="s">
-        <v>149</v>
-      </c>
-      <c r="O36" s="2" t="s">
-        <v>149</v>
-      </c>
-      <c r="P36" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="Q36" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="R36" s="2" t="s">
-        <v>150</v>
-      </c>
-      <c r="S36" s="2">
-        <v>1</v>
-      </c>
+        <v>119</v>
+      </c>
+      <c r="O36" s="2"/>
+      <c r="P36" s="2"/>
+      <c r="Q36" s="2"/>
+      <c r="R36" s="2"/>
+      <c r="S36" s="2"/>
       <c r="T36" s="2"/>
       <c r="U36" s="2"/>
       <c r="V36" s="2"/>
       <c r="W36" s="2"/>
       <c r="X36" s="2"/>
       <c r="Y36" s="2" t="s">
-        <v>111</v>
-      </c>
-      <c r="Z36" s="2"/>
-      <c r="AA36" s="2"/>
-      <c r="AB36" s="2"/>
-      <c r="AC36" s="2"/>
-      <c r="AD36" s="2"/>
-      <c r="AE36" s="2" t="s">
-        <v>151</v>
-      </c>
-      <c r="AF36" s="2" t="s">
-        <v>157</v>
-      </c>
+        <v>211</v>
+      </c>
+      <c r="Z36" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="AA36" s="2" t="s">
+        <v>139</v>
+      </c>
+      <c r="AB36" s="2">
+        <v>8</v>
+      </c>
+      <c r="AC36" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="AD36" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="AE36" s="2"/>
+      <c r="AF36" s="2"/>
       <c r="AG36" s="2"/>
       <c r="AH36" s="2"/>
       <c r="AI36" s="2"/>
-      <c r="AJ36" s="4">
-        <v>183</v>
+      <c r="AJ36">
+        <v>78</v>
       </c>
     </row>
     <row r="37" spans="1:36" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A37" s="2" t="s">
-        <v>158</v>
+        <v>143</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>159</v>
+        <v>144</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>160</v>
+        <v>145</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>160</v>
+        <v>145</v>
       </c>
       <c r="E37" s="2" t="s">
-        <v>161</v>
+        <v>146</v>
       </c>
       <c r="F37" s="2"/>
       <c r="G37" s="2" t="s">
@@ -4498,10 +4513,10 @@
         <v>40</v>
       </c>
       <c r="N37" s="2" t="s">
-        <v>162</v>
+        <v>149</v>
       </c>
       <c r="O37" s="2" t="s">
-        <v>162</v>
+        <v>149</v>
       </c>
       <c r="P37" s="2" t="s">
         <v>42</v>
@@ -4510,7 +4525,7 @@
         <v>43</v>
       </c>
       <c r="R37" s="2" t="s">
-        <v>163</v>
+        <v>150</v>
       </c>
       <c r="S37" s="2">
         <v>1</v>
@@ -4543,19 +4558,19 @@
     </row>
     <row r="38" spans="1:36" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A38" s="2" t="s">
-        <v>164</v>
+        <v>153</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>165</v>
+        <v>154</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>166</v>
+        <v>155</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>166</v>
+        <v>155</v>
       </c>
       <c r="E38" s="2" t="s">
-        <v>167</v>
+        <v>156</v>
       </c>
       <c r="F38" s="2"/>
       <c r="G38" s="2" t="s">
@@ -4576,10 +4591,10 @@
         <v>40</v>
       </c>
       <c r="N38" s="2" t="s">
-        <v>162</v>
+        <v>149</v>
       </c>
       <c r="O38" s="2" t="s">
-        <v>162</v>
+        <v>149</v>
       </c>
       <c r="P38" s="2" t="s">
         <v>42</v>
@@ -4588,7 +4603,7 @@
         <v>43</v>
       </c>
       <c r="R38" s="2" t="s">
-        <v>163</v>
+        <v>150</v>
       </c>
       <c r="S38" s="2">
         <v>1</v>
@@ -4621,19 +4636,19 @@
     </row>
     <row r="39" spans="1:36" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A39" s="2" t="s">
-        <v>168</v>
+        <v>158</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>169</v>
+        <v>159</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>170</v>
+        <v>160</v>
       </c>
       <c r="D39" s="2" t="s">
-        <v>170</v>
+        <v>160</v>
       </c>
       <c r="E39" s="2" t="s">
-        <v>171</v>
+        <v>161</v>
       </c>
       <c r="F39" s="2"/>
       <c r="G39" s="2" t="s">
@@ -4654,10 +4669,10 @@
         <v>40</v>
       </c>
       <c r="N39" s="2" t="s">
-        <v>172</v>
+        <v>162</v>
       </c>
       <c r="O39" s="2" t="s">
-        <v>172</v>
+        <v>162</v>
       </c>
       <c r="P39" s="2" t="s">
         <v>42</v>
@@ -4666,7 +4681,7 @@
         <v>43</v>
       </c>
       <c r="R39" s="2" t="s">
-        <v>173</v>
+        <v>163</v>
       </c>
       <c r="S39" s="2">
         <v>1</v>
@@ -4699,19 +4714,19 @@
     </row>
     <row r="40" spans="1:36" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A40" s="2" t="s">
-        <v>174</v>
+        <v>164</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>175</v>
+        <v>165</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>176</v>
+        <v>166</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>176</v>
+        <v>166</v>
       </c>
       <c r="E40" s="2" t="s">
-        <v>177</v>
+        <v>167</v>
       </c>
       <c r="F40" s="2"/>
       <c r="G40" s="2" t="s">
@@ -4732,10 +4747,10 @@
         <v>40</v>
       </c>
       <c r="N40" s="2" t="s">
-        <v>172</v>
+        <v>162</v>
       </c>
       <c r="O40" s="2" t="s">
-        <v>172</v>
+        <v>162</v>
       </c>
       <c r="P40" s="2" t="s">
         <v>42</v>
@@ -4744,7 +4759,7 @@
         <v>43</v>
       </c>
       <c r="R40" s="2" t="s">
-        <v>173</v>
+        <v>163</v>
       </c>
       <c r="S40" s="2">
         <v>1</v>
@@ -4777,19 +4792,19 @@
     </row>
     <row r="41" spans="1:36" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A41" s="2" t="s">
-        <v>178</v>
+        <v>168</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>179</v>
+        <v>169</v>
       </c>
       <c r="C41" s="2" t="s">
-        <v>180</v>
+        <v>170</v>
       </c>
       <c r="D41" s="2" t="s">
-        <v>180</v>
+        <v>170</v>
       </c>
       <c r="E41" s="2" t="s">
-        <v>181</v>
+        <v>171</v>
       </c>
       <c r="F41" s="2"/>
       <c r="G41" s="2" t="s">
@@ -4810,10 +4825,10 @@
         <v>40</v>
       </c>
       <c r="N41" s="2" t="s">
-        <v>149</v>
+        <v>172</v>
       </c>
       <c r="O41" s="2" t="s">
-        <v>149</v>
+        <v>172</v>
       </c>
       <c r="P41" s="2" t="s">
         <v>42</v>
@@ -4822,7 +4837,7 @@
         <v>43</v>
       </c>
       <c r="R41" s="2" t="s">
-        <v>150</v>
+        <v>173</v>
       </c>
       <c r="S41" s="2">
         <v>1</v>
@@ -4833,7 +4848,7 @@
       <c r="W41" s="2"/>
       <c r="X41" s="2"/>
       <c r="Y41" s="2" t="s">
-        <v>182</v>
+        <v>111</v>
       </c>
       <c r="Z41" s="2"/>
       <c r="AA41" s="2"/>
@@ -4850,24 +4865,24 @@
       <c r="AH41" s="2"/>
       <c r="AI41" s="2"/>
       <c r="AJ41" s="4">
-        <v>184</v>
+        <v>183</v>
       </c>
     </row>
     <row r="42" spans="1:36" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A42" s="2" t="s">
-        <v>183</v>
+        <v>174</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>184</v>
+        <v>175</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>185</v>
+        <v>176</v>
       </c>
       <c r="D42" s="2" t="s">
-        <v>185</v>
+        <v>176</v>
       </c>
       <c r="E42" s="2" t="s">
-        <v>186</v>
+        <v>177</v>
       </c>
       <c r="F42" s="2"/>
       <c r="G42" s="2" t="s">
@@ -4888,10 +4903,10 @@
         <v>40</v>
       </c>
       <c r="N42" s="2" t="s">
-        <v>149</v>
+        <v>172</v>
       </c>
       <c r="O42" s="2" t="s">
-        <v>149</v>
+        <v>172</v>
       </c>
       <c r="P42" s="2" t="s">
         <v>42</v>
@@ -4900,7 +4915,7 @@
         <v>43</v>
       </c>
       <c r="R42" s="2" t="s">
-        <v>150</v>
+        <v>173</v>
       </c>
       <c r="S42" s="2">
         <v>1</v>
@@ -4911,7 +4926,7 @@
       <c r="W42" s="2"/>
       <c r="X42" s="2"/>
       <c r="Y42" s="2" t="s">
-        <v>182</v>
+        <v>111</v>
       </c>
       <c r="Z42" s="2"/>
       <c r="AA42" s="2"/>
@@ -4928,24 +4943,24 @@
       <c r="AH42" s="2"/>
       <c r="AI42" s="2"/>
       <c r="AJ42" s="4">
-        <v>184</v>
+        <v>183</v>
       </c>
     </row>
     <row r="43" spans="1:36" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A43" s="2" t="s">
-        <v>187</v>
+        <v>178</v>
       </c>
       <c r="B43" s="2" t="s">
-        <v>188</v>
+        <v>179</v>
       </c>
       <c r="C43" s="2" t="s">
-        <v>185</v>
+        <v>180</v>
       </c>
       <c r="D43" s="2" t="s">
-        <v>185</v>
+        <v>180</v>
       </c>
       <c r="E43" s="2" t="s">
-        <v>186</v>
+        <v>181</v>
       </c>
       <c r="F43" s="2"/>
       <c r="G43" s="2" t="s">
@@ -5000,7 +5015,7 @@
         <v>151</v>
       </c>
       <c r="AF43" s="2" t="s">
-        <v>157</v>
+        <v>152</v>
       </c>
       <c r="AG43" s="2"/>
       <c r="AH43" s="2"/>
@@ -5011,19 +5026,19 @@
     </row>
     <row r="44" spans="1:36" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A44" s="2" t="s">
-        <v>189</v>
+        <v>183</v>
       </c>
       <c r="B44" s="2" t="s">
-        <v>190</v>
+        <v>184</v>
       </c>
       <c r="C44" s="2" t="s">
-        <v>191</v>
+        <v>185</v>
       </c>
       <c r="D44" s="2" t="s">
-        <v>191</v>
+        <v>185</v>
       </c>
       <c r="E44" s="2" t="s">
-        <v>192</v>
+        <v>186</v>
       </c>
       <c r="F44" s="2"/>
       <c r="G44" s="2" t="s">
@@ -5044,10 +5059,10 @@
         <v>40</v>
       </c>
       <c r="N44" s="2" t="s">
-        <v>162</v>
+        <v>149</v>
       </c>
       <c r="O44" s="2" t="s">
-        <v>162</v>
+        <v>149</v>
       </c>
       <c r="P44" s="2" t="s">
         <v>42</v>
@@ -5056,7 +5071,7 @@
         <v>43</v>
       </c>
       <c r="R44" s="2" t="s">
-        <v>163</v>
+        <v>150</v>
       </c>
       <c r="S44" s="2">
         <v>1</v>
@@ -5078,7 +5093,7 @@
         <v>151</v>
       </c>
       <c r="AF44" s="2" t="s">
-        <v>152</v>
+        <v>157</v>
       </c>
       <c r="AG44" s="2"/>
       <c r="AH44" s="2"/>
@@ -5089,19 +5104,19 @@
     </row>
     <row r="45" spans="1:36" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A45" s="2" t="s">
-        <v>193</v>
+        <v>187</v>
       </c>
       <c r="B45" s="2" t="s">
-        <v>194</v>
+        <v>188</v>
       </c>
       <c r="C45" s="2" t="s">
-        <v>195</v>
+        <v>185</v>
       </c>
       <c r="D45" s="2" t="s">
-        <v>195</v>
+        <v>185</v>
       </c>
       <c r="E45" s="2" t="s">
-        <v>196</v>
+        <v>186</v>
       </c>
       <c r="F45" s="2"/>
       <c r="G45" s="2" t="s">
@@ -5122,10 +5137,10 @@
         <v>40</v>
       </c>
       <c r="N45" s="2" t="s">
-        <v>162</v>
+        <v>149</v>
       </c>
       <c r="O45" s="2" t="s">
-        <v>162</v>
+        <v>149</v>
       </c>
       <c r="P45" s="2" t="s">
         <v>42</v>
@@ -5134,7 +5149,7 @@
         <v>43</v>
       </c>
       <c r="R45" s="2" t="s">
-        <v>163</v>
+        <v>150</v>
       </c>
       <c r="S45" s="2">
         <v>1</v>
@@ -5167,19 +5182,19 @@
     </row>
     <row r="46" spans="1:36" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A46" s="2" t="s">
-        <v>197</v>
+        <v>189</v>
       </c>
       <c r="B46" s="2" t="s">
-        <v>198</v>
+        <v>190</v>
       </c>
       <c r="C46" s="2" t="s">
-        <v>195</v>
+        <v>191</v>
       </c>
       <c r="D46" s="2" t="s">
-        <v>195</v>
+        <v>191</v>
       </c>
       <c r="E46" s="2" t="s">
-        <v>196</v>
+        <v>192</v>
       </c>
       <c r="F46" s="2"/>
       <c r="G46" s="2" t="s">
@@ -5234,7 +5249,7 @@
         <v>151</v>
       </c>
       <c r="AF46" s="2" t="s">
-        <v>157</v>
+        <v>152</v>
       </c>
       <c r="AG46" s="2"/>
       <c r="AH46" s="2"/>
@@ -5245,19 +5260,19 @@
     </row>
     <row r="47" spans="1:36" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A47" s="2" t="s">
-        <v>199</v>
+        <v>193</v>
       </c>
       <c r="B47" s="2" t="s">
-        <v>200</v>
+        <v>194</v>
       </c>
       <c r="C47" s="2" t="s">
-        <v>201</v>
+        <v>195</v>
       </c>
       <c r="D47" s="2" t="s">
-        <v>201</v>
+        <v>195</v>
       </c>
       <c r="E47" s="2" t="s">
-        <v>202</v>
+        <v>196</v>
       </c>
       <c r="F47" s="2"/>
       <c r="G47" s="2" t="s">
@@ -5278,10 +5293,10 @@
         <v>40</v>
       </c>
       <c r="N47" s="2" t="s">
-        <v>172</v>
+        <v>162</v>
       </c>
       <c r="O47" s="2" t="s">
-        <v>172</v>
+        <v>162</v>
       </c>
       <c r="P47" s="2" t="s">
         <v>42</v>
@@ -5290,7 +5305,7 @@
         <v>43</v>
       </c>
       <c r="R47" s="2" t="s">
-        <v>173</v>
+        <v>163</v>
       </c>
       <c r="S47" s="2">
         <v>1</v>
@@ -5312,7 +5327,7 @@
         <v>151</v>
       </c>
       <c r="AF47" s="2" t="s">
-        <v>152</v>
+        <v>157</v>
       </c>
       <c r="AG47" s="2"/>
       <c r="AH47" s="2"/>
@@ -5323,19 +5338,19 @@
     </row>
     <row r="48" spans="1:36" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A48" s="2" t="s">
-        <v>203</v>
+        <v>197</v>
       </c>
       <c r="B48" s="2" t="s">
-        <v>204</v>
+        <v>198</v>
       </c>
       <c r="C48" s="2" t="s">
-        <v>205</v>
+        <v>195</v>
       </c>
       <c r="D48" s="2" t="s">
-        <v>205</v>
+        <v>195</v>
       </c>
       <c r="E48" s="2" t="s">
-        <v>206</v>
+        <v>196</v>
       </c>
       <c r="F48" s="2"/>
       <c r="G48" s="2" t="s">
@@ -5356,10 +5371,10 @@
         <v>40</v>
       </c>
       <c r="N48" s="2" t="s">
-        <v>172</v>
+        <v>162</v>
       </c>
       <c r="O48" s="2" t="s">
-        <v>172</v>
+        <v>162</v>
       </c>
       <c r="P48" s="2" t="s">
         <v>42</v>
@@ -5368,7 +5383,7 @@
         <v>43</v>
       </c>
       <c r="R48" s="2" t="s">
-        <v>173</v>
+        <v>163</v>
       </c>
       <c r="S48" s="2">
         <v>1</v>
@@ -5401,19 +5416,19 @@
     </row>
     <row r="49" spans="1:36" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A49" s="2" t="s">
-        <v>207</v>
+        <v>199</v>
       </c>
       <c r="B49" s="2" t="s">
-        <v>208</v>
+        <v>200</v>
       </c>
       <c r="C49" s="2" t="s">
-        <v>209</v>
+        <v>201</v>
       </c>
       <c r="D49" s="2" t="s">
-        <v>209</v>
+        <v>201</v>
       </c>
       <c r="E49" s="2" t="s">
-        <v>210</v>
+        <v>202</v>
       </c>
       <c r="F49" s="2"/>
       <c r="G49" s="2" t="s">
@@ -5434,10 +5449,10 @@
         <v>40</v>
       </c>
       <c r="N49" s="2" t="s">
-        <v>162</v>
+        <v>172</v>
       </c>
       <c r="O49" s="2" t="s">
-        <v>162</v>
+        <v>172</v>
       </c>
       <c r="P49" s="2" t="s">
         <v>42</v>
@@ -5446,7 +5461,7 @@
         <v>43</v>
       </c>
       <c r="R49" s="2" t="s">
-        <v>163</v>
+        <v>173</v>
       </c>
       <c r="S49" s="2">
         <v>1</v>
@@ -5457,7 +5472,7 @@
       <c r="W49" s="2"/>
       <c r="X49" s="2"/>
       <c r="Y49" s="2" t="s">
-        <v>211</v>
+        <v>182</v>
       </c>
       <c r="Z49" s="2"/>
       <c r="AA49" s="2"/>
@@ -5474,24 +5489,24 @@
       <c r="AH49" s="2"/>
       <c r="AI49" s="2"/>
       <c r="AJ49" s="4">
-        <v>185</v>
+        <v>184</v>
       </c>
     </row>
     <row r="50" spans="1:36" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A50" s="2" t="s">
-        <v>212</v>
+        <v>203</v>
       </c>
       <c r="B50" s="2" t="s">
-        <v>213</v>
+        <v>204</v>
       </c>
       <c r="C50" s="2" t="s">
-        <v>214</v>
+        <v>205</v>
       </c>
       <c r="D50" s="2" t="s">
-        <v>214</v>
+        <v>205</v>
       </c>
       <c r="E50" s="2" t="s">
-        <v>215</v>
+        <v>206</v>
       </c>
       <c r="F50" s="2"/>
       <c r="G50" s="2" t="s">
@@ -5512,10 +5527,10 @@
         <v>40</v>
       </c>
       <c r="N50" s="2" t="s">
-        <v>162</v>
+        <v>172</v>
       </c>
       <c r="O50" s="2" t="s">
-        <v>162</v>
+        <v>172</v>
       </c>
       <c r="P50" s="2" t="s">
         <v>42</v>
@@ -5524,7 +5539,7 @@
         <v>43</v>
       </c>
       <c r="R50" s="2" t="s">
-        <v>163</v>
+        <v>173</v>
       </c>
       <c r="S50" s="2">
         <v>1</v>
@@ -5535,7 +5550,7 @@
       <c r="W50" s="2"/>
       <c r="X50" s="2"/>
       <c r="Y50" s="2" t="s">
-        <v>211</v>
+        <v>182</v>
       </c>
       <c r="Z50" s="2"/>
       <c r="AA50" s="2"/>
@@ -5552,24 +5567,24 @@
       <c r="AH50" s="2"/>
       <c r="AI50" s="2"/>
       <c r="AJ50" s="4">
-        <v>185</v>
+        <v>184</v>
       </c>
     </row>
     <row r="51" spans="1:36" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A51" s="2" t="s">
-        <v>216</v>
+        <v>207</v>
       </c>
       <c r="B51" s="2" t="s">
-        <v>217</v>
+        <v>208</v>
       </c>
       <c r="C51" s="2" t="s">
-        <v>218</v>
+        <v>209</v>
       </c>
       <c r="D51" s="2" t="s">
-        <v>218</v>
+        <v>209</v>
       </c>
       <c r="E51" s="2" t="s">
-        <v>219</v>
+        <v>210</v>
       </c>
       <c r="F51" s="2"/>
       <c r="G51" s="2" t="s">
@@ -5590,10 +5605,10 @@
         <v>40</v>
       </c>
       <c r="N51" s="2" t="s">
-        <v>172</v>
+        <v>162</v>
       </c>
       <c r="O51" s="2" t="s">
-        <v>172</v>
+        <v>162</v>
       </c>
       <c r="P51" s="2" t="s">
         <v>42</v>
@@ -5602,7 +5617,7 @@
         <v>43</v>
       </c>
       <c r="R51" s="2" t="s">
-        <v>173</v>
+        <v>163</v>
       </c>
       <c r="S51" s="2">
         <v>1</v>
@@ -5635,19 +5650,19 @@
     </row>
     <row r="52" spans="1:36" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A52" s="2" t="s">
-        <v>220</v>
+        <v>212</v>
       </c>
       <c r="B52" s="2" t="s">
-        <v>221</v>
+        <v>213</v>
       </c>
       <c r="C52" s="2" t="s">
-        <v>222</v>
+        <v>214</v>
       </c>
       <c r="D52" s="2" t="s">
-        <v>222</v>
+        <v>214</v>
       </c>
       <c r="E52" s="2" t="s">
-        <v>223</v>
+        <v>215</v>
       </c>
       <c r="F52" s="2"/>
       <c r="G52" s="2" t="s">
@@ -5668,10 +5683,10 @@
         <v>40</v>
       </c>
       <c r="N52" s="2" t="s">
-        <v>172</v>
+        <v>162</v>
       </c>
       <c r="O52" s="2" t="s">
-        <v>172</v>
+        <v>162</v>
       </c>
       <c r="P52" s="2" t="s">
         <v>42</v>
@@ -5680,7 +5695,7 @@
         <v>43</v>
       </c>
       <c r="R52" s="2" t="s">
-        <v>173</v>
+        <v>163</v>
       </c>
       <c r="S52" s="2">
         <v>1</v>
@@ -5713,19 +5728,19 @@
     </row>
     <row r="53" spans="1:36" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A53" s="2" t="s">
-        <v>224</v>
+        <v>216</v>
       </c>
       <c r="B53" s="2" t="s">
-        <v>225</v>
+        <v>217</v>
       </c>
       <c r="C53" s="2" t="s">
-        <v>222</v>
+        <v>218</v>
       </c>
       <c r="D53" s="2" t="s">
-        <v>222</v>
+        <v>218</v>
       </c>
       <c r="E53" s="2" t="s">
-        <v>223</v>
+        <v>219</v>
       </c>
       <c r="F53" s="2"/>
       <c r="G53" s="2" t="s">
@@ -5780,7 +5795,7 @@
         <v>151</v>
       </c>
       <c r="AF53" s="2" t="s">
-        <v>157</v>
+        <v>152</v>
       </c>
       <c r="AG53" s="2"/>
       <c r="AH53" s="2"/>
@@ -5791,19 +5806,19 @@
     </row>
     <row r="54" spans="1:36" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A54" s="2" t="s">
-        <v>226</v>
+        <v>220</v>
       </c>
       <c r="B54" s="2" t="s">
-        <v>227</v>
+        <v>221</v>
       </c>
       <c r="C54" s="2" t="s">
-        <v>228</v>
+        <v>222</v>
       </c>
       <c r="D54" s="2" t="s">
-        <v>228</v>
+        <v>222</v>
       </c>
       <c r="E54" s="2" t="s">
-        <v>229</v>
+        <v>223</v>
       </c>
       <c r="F54" s="2"/>
       <c r="G54" s="2" t="s">
@@ -5824,10 +5839,10 @@
         <v>40</v>
       </c>
       <c r="N54" s="2" t="s">
-        <v>149</v>
+        <v>172</v>
       </c>
       <c r="O54" s="2" t="s">
-        <v>149</v>
+        <v>172</v>
       </c>
       <c r="P54" s="2" t="s">
         <v>42</v>
@@ -5836,7 +5851,7 @@
         <v>43</v>
       </c>
       <c r="R54" s="2" t="s">
-        <v>150</v>
+        <v>173</v>
       </c>
       <c r="S54" s="2">
         <v>1</v>
@@ -5858,7 +5873,7 @@
         <v>151</v>
       </c>
       <c r="AF54" s="2" t="s">
-        <v>152</v>
+        <v>157</v>
       </c>
       <c r="AG54" s="2"/>
       <c r="AH54" s="2"/>
@@ -5869,19 +5884,19 @@
     </row>
     <row r="55" spans="1:36" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A55" s="2" t="s">
-        <v>230</v>
+        <v>224</v>
       </c>
       <c r="B55" s="2" t="s">
-        <v>231</v>
+        <v>225</v>
       </c>
       <c r="C55" s="2" t="s">
-        <v>232</v>
+        <v>222</v>
       </c>
       <c r="D55" s="2" t="s">
-        <v>232</v>
+        <v>222</v>
       </c>
       <c r="E55" s="2" t="s">
-        <v>233</v>
+        <v>223</v>
       </c>
       <c r="F55" s="2"/>
       <c r="G55" s="2" t="s">
@@ -5902,10 +5917,10 @@
         <v>40</v>
       </c>
       <c r="N55" s="2" t="s">
-        <v>149</v>
+        <v>172</v>
       </c>
       <c r="O55" s="2" t="s">
-        <v>149</v>
+        <v>172</v>
       </c>
       <c r="P55" s="2" t="s">
         <v>42</v>
@@ -5914,7 +5929,7 @@
         <v>43</v>
       </c>
       <c r="R55" s="2" t="s">
-        <v>150</v>
+        <v>173</v>
       </c>
       <c r="S55" s="2">
         <v>1</v>
@@ -5947,19 +5962,19 @@
     </row>
     <row r="56" spans="1:36" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A56" s="2" t="s">
-        <v>234</v>
+        <v>226</v>
       </c>
       <c r="B56" s="2" t="s">
-        <v>235</v>
+        <v>227</v>
       </c>
       <c r="C56" s="2" t="s">
-        <v>232</v>
+        <v>228</v>
       </c>
       <c r="D56" s="2" t="s">
-        <v>232</v>
+        <v>228</v>
       </c>
       <c r="E56" s="2" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
       <c r="F56" s="2"/>
       <c r="G56" s="2" t="s">
@@ -6014,7 +6029,7 @@
         <v>151</v>
       </c>
       <c r="AF56" s="2" t="s">
-        <v>157</v>
+        <v>152</v>
       </c>
       <c r="AG56" s="2"/>
       <c r="AH56" s="2"/>
@@ -6025,147 +6040,175 @@
     </row>
     <row r="57" spans="1:36" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A57" s="2" t="s">
-        <v>236</v>
+        <v>230</v>
       </c>
       <c r="B57" s="2" t="s">
-        <v>237</v>
+        <v>231</v>
       </c>
       <c r="C57" s="2" t="s">
-        <v>238</v>
+        <v>232</v>
       </c>
       <c r="D57" s="2" t="s">
-        <v>238</v>
+        <v>232</v>
       </c>
       <c r="E57" s="2" t="s">
-        <v>239</v>
+        <v>233</v>
       </c>
       <c r="F57" s="2"/>
       <c r="G57" s="2" t="s">
-        <v>240</v>
+        <v>147</v>
       </c>
       <c r="H57" s="2" t="s">
-        <v>241</v>
+        <v>148</v>
       </c>
       <c r="I57" s="2" t="s">
-        <v>242</v>
-      </c>
-      <c r="J57" s="2"/>
+        <v>36</v>
+      </c>
+      <c r="J57" s="2" t="s">
+        <v>55</v>
+      </c>
       <c r="K57" s="2"/>
       <c r="L57" s="2"/>
-      <c r="M57" s="2"/>
-      <c r="N57" s="2"/>
-      <c r="O57" s="2"/>
-      <c r="P57" s="2"/>
-      <c r="Q57" s="2"/>
-      <c r="R57" s="2"/>
-      <c r="S57" s="2"/>
+      <c r="M57" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="N57" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="O57" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="P57" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="Q57" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="R57" s="2" t="s">
+        <v>150</v>
+      </c>
+      <c r="S57" s="2">
+        <v>1</v>
+      </c>
       <c r="T57" s="2"/>
       <c r="U57" s="2"/>
       <c r="V57" s="2"/>
       <c r="W57" s="2"/>
       <c r="X57" s="2"/>
-      <c r="Y57" s="2"/>
+      <c r="Y57" s="2" t="s">
+        <v>211</v>
+      </c>
       <c r="Z57" s="2"/>
       <c r="AA57" s="2"/>
       <c r="AB57" s="2"/>
       <c r="AC57" s="2"/>
       <c r="AD57" s="2"/>
-      <c r="AE57" s="2"/>
+      <c r="AE57" s="2" t="s">
+        <v>151</v>
+      </c>
       <c r="AF57" s="2" t="s">
         <v>157</v>
       </c>
-      <c r="AG57" s="2" t="s">
-        <v>139</v>
-      </c>
-      <c r="AH57" s="2" t="s">
-        <v>243</v>
-      </c>
-      <c r="AI57" s="2" t="s">
-        <v>244</v>
-      </c>
+      <c r="AG57" s="2"/>
+      <c r="AH57" s="2"/>
+      <c r="AI57" s="2"/>
       <c r="AJ57" s="4">
-        <v>186</v>
+        <v>185</v>
       </c>
     </row>
     <row r="58" spans="1:36" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A58" s="2" t="s">
-        <v>245</v>
+        <v>234</v>
       </c>
       <c r="B58" s="2" t="s">
-        <v>246</v>
+        <v>235</v>
       </c>
       <c r="C58" s="2" t="s">
-        <v>247</v>
+        <v>232</v>
       </c>
       <c r="D58" s="2" t="s">
-        <v>247</v>
+        <v>232</v>
       </c>
       <c r="E58" s="2" t="s">
-        <v>248</v>
+        <v>233</v>
       </c>
       <c r="F58" s="2"/>
       <c r="G58" s="2" t="s">
-        <v>240</v>
+        <v>147</v>
       </c>
       <c r="H58" s="2" t="s">
-        <v>241</v>
+        <v>148</v>
       </c>
       <c r="I58" s="2" t="s">
-        <v>242</v>
-      </c>
-      <c r="J58" s="2"/>
+        <v>36</v>
+      </c>
+      <c r="J58" s="2" t="s">
+        <v>55</v>
+      </c>
       <c r="K58" s="2"/>
       <c r="L58" s="2"/>
-      <c r="M58" s="2"/>
-      <c r="N58" s="2"/>
-      <c r="O58" s="2"/>
-      <c r="P58" s="2"/>
-      <c r="Q58" s="2"/>
-      <c r="R58" s="2"/>
-      <c r="S58" s="2"/>
+      <c r="M58" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="N58" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="O58" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="P58" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="Q58" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="R58" s="2" t="s">
+        <v>150</v>
+      </c>
+      <c r="S58" s="2">
+        <v>1</v>
+      </c>
       <c r="T58" s="2"/>
       <c r="U58" s="2"/>
       <c r="V58" s="2"/>
       <c r="W58" s="2"/>
       <c r="X58" s="2"/>
-      <c r="Y58" s="2"/>
+      <c r="Y58" s="2" t="s">
+        <v>211</v>
+      </c>
       <c r="Z58" s="2"/>
       <c r="AA58" s="2"/>
       <c r="AB58" s="2"/>
       <c r="AC58" s="2"/>
       <c r="AD58" s="2"/>
-      <c r="AE58" s="2"/>
+      <c r="AE58" s="2" t="s">
+        <v>151</v>
+      </c>
       <c r="AF58" s="2" t="s">
         <v>157</v>
       </c>
-      <c r="AG58" s="2" t="s">
-        <v>139</v>
-      </c>
-      <c r="AH58" s="2" t="s">
-        <v>243</v>
-      </c>
-      <c r="AI58" s="2" t="s">
-        <v>249</v>
-      </c>
+      <c r="AG58" s="2"/>
+      <c r="AH58" s="2"/>
+      <c r="AI58" s="2"/>
       <c r="AJ58" s="4">
-        <v>186</v>
+        <v>185</v>
       </c>
     </row>
     <row r="59" spans="1:36" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A59" s="2" t="s">
-        <v>250</v>
+        <v>236</v>
       </c>
       <c r="B59" s="2" t="s">
-        <v>251</v>
+        <v>237</v>
       </c>
       <c r="C59" s="2" t="s">
-        <v>252</v>
+        <v>238</v>
       </c>
       <c r="D59" s="2" t="s">
-        <v>252</v>
+        <v>238</v>
       </c>
       <c r="E59" s="2" t="s">
-        <v>253</v>
+        <v>239</v>
       </c>
       <c r="F59" s="2"/>
       <c r="G59" s="2" t="s">
@@ -6209,13 +6252,142 @@
         <v>243</v>
       </c>
       <c r="AI59" s="2" t="s">
-        <v>254</v>
+        <v>244</v>
       </c>
       <c r="AJ59" s="4">
         <v>186</v>
       </c>
     </row>
+    <row r="60" spans="1:36" s="4" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A60" s="2" t="s">
+        <v>245</v>
+      </c>
+      <c r="B60" s="2" t="s">
+        <v>246</v>
+      </c>
+      <c r="C60" s="2" t="s">
+        <v>247</v>
+      </c>
+      <c r="D60" s="2" t="s">
+        <v>247</v>
+      </c>
+      <c r="E60" s="2" t="s">
+        <v>248</v>
+      </c>
+      <c r="F60" s="2"/>
+      <c r="G60" s="2" t="s">
+        <v>240</v>
+      </c>
+      <c r="H60" s="2" t="s">
+        <v>241</v>
+      </c>
+      <c r="I60" s="2" t="s">
+        <v>242</v>
+      </c>
+      <c r="J60" s="2"/>
+      <c r="K60" s="2"/>
+      <c r="L60" s="2"/>
+      <c r="M60" s="2"/>
+      <c r="N60" s="2"/>
+      <c r="O60" s="2"/>
+      <c r="P60" s="2"/>
+      <c r="Q60" s="2"/>
+      <c r="R60" s="2"/>
+      <c r="S60" s="2"/>
+      <c r="T60" s="2"/>
+      <c r="U60" s="2"/>
+      <c r="V60" s="2"/>
+      <c r="W60" s="2"/>
+      <c r="X60" s="2"/>
+      <c r="Y60" s="2"/>
+      <c r="Z60" s="2"/>
+      <c r="AA60" s="2"/>
+      <c r="AB60" s="2"/>
+      <c r="AC60" s="2"/>
+      <c r="AD60" s="2"/>
+      <c r="AE60" s="2"/>
+      <c r="AF60" s="2" t="s">
+        <v>157</v>
+      </c>
+      <c r="AG60" s="2" t="s">
+        <v>139</v>
+      </c>
+      <c r="AH60" s="2" t="s">
+        <v>243</v>
+      </c>
+      <c r="AI60" s="2" t="s">
+        <v>249</v>
+      </c>
+      <c r="AJ60" s="4">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="61" spans="1:36" s="4" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A61" s="2" t="s">
+        <v>250</v>
+      </c>
+      <c r="B61" s="2" t="s">
+        <v>251</v>
+      </c>
+      <c r="C61" s="2" t="s">
+        <v>252</v>
+      </c>
+      <c r="D61" s="2" t="s">
+        <v>252</v>
+      </c>
+      <c r="E61" s="2" t="s">
+        <v>253</v>
+      </c>
+      <c r="F61" s="2"/>
+      <c r="G61" s="2" t="s">
+        <v>240</v>
+      </c>
+      <c r="H61" s="2" t="s">
+        <v>241</v>
+      </c>
+      <c r="I61" s="2" t="s">
+        <v>242</v>
+      </c>
+      <c r="J61" s="2"/>
+      <c r="K61" s="2"/>
+      <c r="L61" s="2"/>
+      <c r="M61" s="2"/>
+      <c r="N61" s="2"/>
+      <c r="O61" s="2"/>
+      <c r="P61" s="2"/>
+      <c r="Q61" s="2"/>
+      <c r="R61" s="2"/>
+      <c r="S61" s="2"/>
+      <c r="T61" s="2"/>
+      <c r="U61" s="2"/>
+      <c r="V61" s="2"/>
+      <c r="W61" s="2"/>
+      <c r="X61" s="2"/>
+      <c r="Y61" s="2"/>
+      <c r="Z61" s="2"/>
+      <c r="AA61" s="2"/>
+      <c r="AB61" s="2"/>
+      <c r="AC61" s="2"/>
+      <c r="AD61" s="2"/>
+      <c r="AE61" s="2"/>
+      <c r="AF61" s="2" t="s">
+        <v>157</v>
+      </c>
+      <c r="AG61" s="2" t="s">
+        <v>139</v>
+      </c>
+      <c r="AH61" s="2" t="s">
+        <v>243</v>
+      </c>
+      <c r="AI61" s="2" t="s">
+        <v>254</v>
+      </c>
+      <c r="AJ61" s="4">
+        <v>186</v>
+      </c>
+    </row>
   </sheetData>
+  <autoFilter ref="A1:AJ61" xr:uid="{F51B6AD5-20E5-4E41-9D87-5C366E73940C}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>

--- a/source/connector_service.xlsx
+++ b/source/connector_service.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\enterprise\omega\Папки отделов\Департамент закупівель та логістики\Відділ реінжинірингу процесів закупівель\Master data\З'єднувач\обработка\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{42C4A13E-3789-457F-B1D2-A11F3EB39553}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EE77455D-AAF5-4F7F-A779-081E44FA9EAF}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="11625" xr2:uid="{CE2CFF51-9F38-4EC7-9E81-657A284ABED4}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="Аркуш1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Аркуш1!$A$1:$AJ$61</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Аркуш1!$A$1:$AJ$62</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1021" uniqueCount="286">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1037" uniqueCount="288">
   <si>
     <t>Номер карточки</t>
   </si>
@@ -1408,6 +1408,12 @@
   </si>
   <si>
     <t>_DK-11.3513110</t>
+  </si>
+  <si>
+    <t>_69951278405</t>
+  </si>
+  <si>
+    <t>_RD-11.3513110</t>
   </si>
 </sst>
 </file>
@@ -1794,7 +1800,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A3118E0D-448D-4EEB-9348-1247B3113B2C}">
-  <dimension ref="A1:AJ61"/>
+  <dimension ref="A1:AJ62"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="23" customWidth="1"/>
@@ -2822,26 +2828,24 @@
     </row>
     <row r="14" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
-        <v>66</v>
+        <v>286</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>67</v>
+        <v>287</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>68</v>
+        <v>32</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="E14" s="2" t="s">
-        <v>69</v>
-      </c>
+        <v>32</v>
+      </c>
+      <c r="E14" s="2"/>
       <c r="F14" s="2"/>
       <c r="G14" s="2" t="s">
-        <v>70</v>
+        <v>34</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>71</v>
+        <v>35</v>
       </c>
       <c r="I14" s="2" t="s">
         <v>36</v>
@@ -2849,8 +2853,12 @@
       <c r="J14" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="K14" s="2"/>
-      <c r="L14" s="2"/>
+      <c r="K14" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="L14" s="2" t="s">
+        <v>39</v>
+      </c>
       <c r="M14" s="2" t="s">
         <v>40</v>
       </c>
@@ -2872,21 +2880,11 @@
       <c r="S14" s="2">
         <v>1.5</v>
       </c>
-      <c r="T14" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="U14" s="2" t="s">
-        <v>73</v>
-      </c>
-      <c r="V14" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="W14" s="2" t="s">
-        <v>74</v>
-      </c>
-      <c r="X14" s="2" t="s">
-        <v>75</v>
-      </c>
+      <c r="T14" s="2"/>
+      <c r="U14" s="2"/>
+      <c r="V14" s="2"/>
+      <c r="W14" s="2"/>
+      <c r="X14" s="2"/>
       <c r="Y14" s="2"/>
       <c r="Z14" s="2"/>
       <c r="AA14" s="2"/>
@@ -2899,24 +2897,24 @@
       <c r="AH14" s="2"/>
       <c r="AI14" s="2"/>
       <c r="AJ14">
-        <v>130</v>
+        <v>129</v>
       </c>
     </row>
     <row r="15" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
-        <v>76</v>
+        <v>66</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>77</v>
+        <v>67</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>78</v>
+        <v>68</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>78</v>
+        <v>68</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>79</v>
+        <v>69</v>
       </c>
       <c r="F15" s="2"/>
       <c r="G15" s="2" t="s">
@@ -2937,10 +2935,10 @@
         <v>40</v>
       </c>
       <c r="N15" s="2" t="s">
-        <v>80</v>
+        <v>41</v>
       </c>
       <c r="O15" s="2" t="s">
-        <v>80</v>
+        <v>41</v>
       </c>
       <c r="P15" s="2" t="s">
         <v>42</v>
@@ -2949,7 +2947,7 @@
         <v>43</v>
       </c>
       <c r="R15" s="2" t="s">
-        <v>81</v>
+        <v>44</v>
       </c>
       <c r="S15" s="2">
         <v>1.5</v>
@@ -2986,23 +2984,21 @@
     </row>
     <row r="16" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>83</v>
+        <v>77</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>84</v>
+        <v>78</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>84</v>
+        <v>78</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>85</v>
-      </c>
-      <c r="F16" s="2" t="s">
-        <v>86</v>
-      </c>
+        <v>79</v>
+      </c>
+      <c r="F16" s="2"/>
       <c r="G16" s="2" t="s">
         <v>70</v>
       </c>
@@ -3012,17 +3008,19 @@
       <c r="I16" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="J16" s="2"/>
+      <c r="J16" s="2" t="s">
+        <v>37</v>
+      </c>
       <c r="K16" s="2"/>
       <c r="L16" s="2"/>
       <c r="M16" s="2" t="s">
         <v>40</v>
       </c>
       <c r="N16" s="2" t="s">
-        <v>41</v>
+        <v>80</v>
       </c>
       <c r="O16" s="2" t="s">
-        <v>41</v>
+        <v>80</v>
       </c>
       <c r="P16" s="2" t="s">
         <v>42</v>
@@ -3031,7 +3029,7 @@
         <v>43</v>
       </c>
       <c r="R16" s="2" t="s">
-        <v>44</v>
+        <v>81</v>
       </c>
       <c r="S16" s="2">
         <v>1.5</v>
@@ -3048,7 +3046,9 @@
       <c r="W16" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="X16" s="2"/>
+      <c r="X16" s="2" t="s">
+        <v>75</v>
+      </c>
       <c r="Y16" s="2"/>
       <c r="Z16" s="2"/>
       <c r="AA16" s="2"/>
@@ -3066,19 +3066,19 @@
     </row>
     <row r="17" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
-        <v>87</v>
+        <v>82</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>88</v>
+        <v>83</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>89</v>
+        <v>84</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>89</v>
+        <v>84</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="F17" s="2" t="s">
         <v>86</v>
@@ -3099,10 +3099,10 @@
         <v>40</v>
       </c>
       <c r="N17" s="2" t="s">
-        <v>80</v>
+        <v>41</v>
       </c>
       <c r="O17" s="2" t="s">
-        <v>80</v>
+        <v>41</v>
       </c>
       <c r="P17" s="2" t="s">
         <v>42</v>
@@ -3111,7 +3111,7 @@
         <v>43</v>
       </c>
       <c r="R17" s="2" t="s">
-        <v>81</v>
+        <v>44</v>
       </c>
       <c r="S17" s="2">
         <v>1.5</v>
@@ -3146,19 +3146,19 @@
     </row>
     <row r="18" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="F18" s="2" t="s">
         <v>86</v>
@@ -3208,9 +3208,7 @@
       <c r="W18" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="X18" s="2" t="s">
-        <v>75</v>
-      </c>
+      <c r="X18" s="2"/>
       <c r="Y18" s="2"/>
       <c r="Z18" s="2"/>
       <c r="AA18" s="2"/>
@@ -3228,10 +3226,10 @@
     </row>
     <row r="19" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
-        <v>282</v>
+        <v>91</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>283</v>
+        <v>92</v>
       </c>
       <c r="C19" s="2" t="s">
         <v>93</v>
@@ -3310,19 +3308,19 @@
     </row>
     <row r="20" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
-        <v>95</v>
+        <v>282</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>96</v>
+        <v>283</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>97</v>
+        <v>93</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>97</v>
+        <v>93</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="F20" s="2" t="s">
         <v>86</v>
@@ -3343,10 +3341,10 @@
         <v>40</v>
       </c>
       <c r="N20" s="2" t="s">
-        <v>41</v>
+        <v>80</v>
       </c>
       <c r="O20" s="2" t="s">
-        <v>41</v>
+        <v>80</v>
       </c>
       <c r="P20" s="2" t="s">
         <v>42</v>
@@ -3355,7 +3353,7 @@
         <v>43</v>
       </c>
       <c r="R20" s="2" t="s">
-        <v>44</v>
+        <v>81</v>
       </c>
       <c r="S20" s="2">
         <v>1.5</v>
@@ -3392,21 +3390,23 @@
     </row>
     <row r="21" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>68</v>
+        <v>97</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>68</v>
+        <v>97</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="F21" s="2"/>
+        <v>98</v>
+      </c>
+      <c r="F21" s="2" t="s">
+        <v>86</v>
+      </c>
       <c r="G21" s="2" t="s">
         <v>70</v>
       </c>
@@ -3416,9 +3416,7 @@
       <c r="I21" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="J21" s="2" t="s">
-        <v>37</v>
-      </c>
+      <c r="J21" s="2"/>
       <c r="K21" s="2"/>
       <c r="L21" s="2"/>
       <c r="M21" s="2" t="s">
@@ -3474,10 +3472,10 @@
     </row>
     <row r="22" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="C22" s="2" t="s">
         <v>68</v>
@@ -3556,26 +3554,26 @@
     </row>
     <row r="23" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>105</v>
+        <v>68</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>105</v>
+        <v>68</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>106</v>
+        <v>69</v>
       </c>
       <c r="F23" s="2"/>
       <c r="G23" s="2" t="s">
-        <v>107</v>
+        <v>70</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>108</v>
+        <v>71</v>
       </c>
       <c r="I23" s="2" t="s">
         <v>36</v>
@@ -3586,63 +3584,71 @@
       <c r="K23" s="2"/>
       <c r="L23" s="2"/>
       <c r="M23" s="2" t="s">
-        <v>109</v>
+        <v>40</v>
       </c>
       <c r="N23" s="2" t="s">
-        <v>110</v>
-      </c>
-      <c r="O23" s="2"/>
-      <c r="P23" s="2"/>
-      <c r="Q23" s="2"/>
-      <c r="R23" s="2"/>
-      <c r="S23" s="2"/>
-      <c r="T23" s="2"/>
-      <c r="U23" s="2"/>
-      <c r="V23" s="2"/>
-      <c r="W23" s="2"/>
-      <c r="X23" s="2"/>
-      <c r="Y23" s="2" t="s">
-        <v>111</v>
-      </c>
-      <c r="Z23" s="2" t="s">
-        <v>112</v>
-      </c>
-      <c r="AA23" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="AB23" s="2">
-        <v>6</v>
-      </c>
-      <c r="AC23" s="2" t="s">
-        <v>113</v>
-      </c>
-      <c r="AD23" s="2" t="s">
-        <v>114</v>
-      </c>
+        <v>41</v>
+      </c>
+      <c r="O23" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="P23" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="Q23" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="R23" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="S23" s="2">
+        <v>1.5</v>
+      </c>
+      <c r="T23" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="U23" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="V23" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="W23" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="X23" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="Y23" s="2"/>
+      <c r="Z23" s="2"/>
+      <c r="AA23" s="2"/>
+      <c r="AB23" s="2"/>
+      <c r="AC23" s="2"/>
+      <c r="AD23" s="2"/>
       <c r="AE23" s="2"/>
       <c r="AF23" s="2"/>
       <c r="AG23" s="2"/>
       <c r="AH23" s="2"/>
       <c r="AI23" s="2"/>
       <c r="AJ23">
-        <v>75</v>
+        <v>130</v>
       </c>
     </row>
     <row r="24" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="s">
-        <v>115</v>
+        <v>103</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>116</v>
+        <v>104</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>117</v>
+        <v>105</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>117</v>
+        <v>105</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>118</v>
+        <v>106</v>
       </c>
       <c r="F24" s="2"/>
       <c r="G24" s="2" t="s">
@@ -3663,7 +3669,7 @@
         <v>109</v>
       </c>
       <c r="N24" s="2" t="s">
-        <v>119</v>
+        <v>110</v>
       </c>
       <c r="O24" s="2"/>
       <c r="P24" s="2"/>
@@ -3685,7 +3691,7 @@
         <v>55</v>
       </c>
       <c r="AB24" s="2">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="AC24" s="2" t="s">
         <v>113</v>
@@ -3704,10 +3710,10 @@
     </row>
     <row r="25" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A25" s="2" t="s">
-        <v>120</v>
+        <v>115</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>121</v>
+        <v>116</v>
       </c>
       <c r="C25" s="2" t="s">
         <v>117</v>
@@ -3778,19 +3784,19 @@
     </row>
     <row r="26" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A26" s="2" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>124</v>
+        <v>117</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>124</v>
+        <v>117</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>125</v>
+        <v>118</v>
       </c>
       <c r="F26" s="2"/>
       <c r="G26" s="2" t="s">
@@ -3803,7 +3809,7 @@
         <v>36</v>
       </c>
       <c r="J26" s="2" t="s">
-        <v>55</v>
+        <v>37</v>
       </c>
       <c r="K26" s="2"/>
       <c r="L26" s="2"/>
@@ -3811,7 +3817,7 @@
         <v>109</v>
       </c>
       <c r="N26" s="2" t="s">
-        <v>110</v>
+        <v>119</v>
       </c>
       <c r="O26" s="2"/>
       <c r="P26" s="2"/>
@@ -3833,7 +3839,7 @@
         <v>55</v>
       </c>
       <c r="AB26" s="2">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AC26" s="2" t="s">
         <v>113</v>
@@ -3847,24 +3853,24 @@
       <c r="AH26" s="2"/>
       <c r="AI26" s="2"/>
       <c r="AJ26">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="27" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A27" s="2" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>128</v>
+        <v>124</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>128</v>
+        <v>124</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>129</v>
+        <v>125</v>
       </c>
       <c r="F27" s="2"/>
       <c r="G27" s="2" t="s">
@@ -3885,7 +3891,7 @@
         <v>109</v>
       </c>
       <c r="N27" s="2" t="s">
-        <v>119</v>
+        <v>110</v>
       </c>
       <c r="O27" s="2"/>
       <c r="P27" s="2"/>
@@ -3907,7 +3913,7 @@
         <v>55</v>
       </c>
       <c r="AB27" s="2">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="AC27" s="2" t="s">
         <v>113</v>
@@ -3926,19 +3932,19 @@
     </row>
     <row r="28" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A28" s="2" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>131</v>
+        <v>127</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="F28" s="2"/>
       <c r="G28" s="2" t="s">
@@ -3959,7 +3965,7 @@
         <v>109</v>
       </c>
       <c r="N28" s="2" t="s">
-        <v>110</v>
+        <v>119</v>
       </c>
       <c r="O28" s="2"/>
       <c r="P28" s="2"/>
@@ -3981,7 +3987,7 @@
         <v>55</v>
       </c>
       <c r="AB28" s="2">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AC28" s="2" t="s">
         <v>113</v>
@@ -4000,19 +4006,19 @@
     </row>
     <row r="29" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A29" s="2" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>260</v>
+        <v>124</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>260</v>
+        <v>124</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>261</v>
+        <v>125</v>
       </c>
       <c r="F29" s="2"/>
       <c r="G29" s="2" t="s">
@@ -4025,7 +4031,7 @@
         <v>36</v>
       </c>
       <c r="J29" s="2" t="s">
-        <v>134</v>
+        <v>55</v>
       </c>
       <c r="K29" s="2"/>
       <c r="L29" s="2"/>
@@ -4046,7 +4052,7 @@
       <c r="W29" s="2"/>
       <c r="X29" s="2"/>
       <c r="Y29" s="2" t="s">
-        <v>211</v>
+        <v>111</v>
       </c>
       <c r="Z29" s="2" t="s">
         <v>112</v>
@@ -4069,24 +4075,24 @@
       <c r="AH29" s="2"/>
       <c r="AI29" s="2"/>
       <c r="AJ29">
-        <v>77</v>
+        <v>76</v>
       </c>
     </row>
     <row r="30" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A30" s="2" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="F30" s="2"/>
       <c r="G30" s="2" t="s">
@@ -4107,7 +4113,7 @@
         <v>109</v>
       </c>
       <c r="N30" s="2" t="s">
-        <v>119</v>
+        <v>110</v>
       </c>
       <c r="O30" s="2"/>
       <c r="P30" s="2"/>
@@ -4129,7 +4135,7 @@
         <v>55</v>
       </c>
       <c r="AB30" s="2">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="AC30" s="2" t="s">
         <v>113</v>
@@ -4148,19 +4154,19 @@
     </row>
     <row r="31" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A31" s="2" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="F31" s="2"/>
       <c r="G31" s="2" t="s">
@@ -4181,7 +4187,7 @@
         <v>109</v>
       </c>
       <c r="N31" s="2" t="s">
-        <v>110</v>
+        <v>119</v>
       </c>
       <c r="O31" s="2"/>
       <c r="P31" s="2"/>
@@ -4200,10 +4206,10 @@
         <v>112</v>
       </c>
       <c r="AA31" s="2" t="s">
-        <v>139</v>
+        <v>55</v>
       </c>
       <c r="AB31" s="2">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AC31" s="2" t="s">
         <v>113</v>
@@ -4217,30 +4223,46 @@
       <c r="AH31" s="2"/>
       <c r="AI31" s="2"/>
       <c r="AJ31">
-        <v>78</v>
+        <v>77</v>
       </c>
     </row>
     <row r="32" spans="1:36" x14ac:dyDescent="0.25">
-      <c r="A32" t="s">
-        <v>268</v>
-      </c>
-      <c r="B32" t="s">
-        <v>269</v>
-      </c>
-      <c r="C32" t="s">
-        <v>276</v>
-      </c>
-      <c r="D32" s="2"/>
-      <c r="E32" s="2"/>
+      <c r="A32" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="B32" s="2" t="s">
+        <v>138</v>
+      </c>
+      <c r="C32" s="2" t="s">
+        <v>264</v>
+      </c>
+      <c r="D32" s="2" t="s">
+        <v>264</v>
+      </c>
+      <c r="E32" s="2" t="s">
+        <v>265</v>
+      </c>
       <c r="F32" s="2"/>
-      <c r="G32" s="2"/>
-      <c r="H32" s="2"/>
-      <c r="I32" s="2"/>
-      <c r="J32" s="2"/>
+      <c r="G32" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="H32" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="I32" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="J32" s="2" t="s">
+        <v>134</v>
+      </c>
       <c r="K32" s="2"/>
       <c r="L32" s="2"/>
-      <c r="M32" s="2"/>
-      <c r="N32" s="2"/>
+      <c r="M32" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="N32" s="2" t="s">
+        <v>110</v>
+      </c>
       <c r="O32" s="2"/>
       <c r="P32" s="2"/>
       <c r="Q32" s="2"/>
@@ -4251,30 +4273,42 @@
       <c r="V32" s="2"/>
       <c r="W32" s="2"/>
       <c r="X32" s="2"/>
-      <c r="Y32" s="2"/>
-      <c r="Z32" s="2"/>
-      <c r="AA32" s="2"/>
-      <c r="AB32" s="2"/>
-      <c r="AC32" s="2"/>
-      <c r="AD32" s="2"/>
+      <c r="Y32" s="2" t="s">
+        <v>211</v>
+      </c>
+      <c r="Z32" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="AA32" s="2" t="s">
+        <v>139</v>
+      </c>
+      <c r="AB32" s="2">
+        <v>6</v>
+      </c>
+      <c r="AC32" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="AD32" s="2" t="s">
+        <v>114</v>
+      </c>
       <c r="AE32" s="2"/>
       <c r="AF32" s="2"/>
       <c r="AG32" s="2"/>
       <c r="AH32" s="2"/>
       <c r="AI32" s="2"/>
       <c r="AJ32">
-        <v>74</v>
+        <v>78</v>
       </c>
     </row>
     <row r="33" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="B33" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="C33" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="D33" s="2"/>
       <c r="E33" s="2"/>
@@ -4314,13 +4348,13 @@
     </row>
     <row r="34" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="B34" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="C34" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="D34" s="2"/>
       <c r="E34" s="2"/>
@@ -4360,13 +4394,13 @@
     </row>
     <row r="35" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="B35" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="C35" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="D35" s="2"/>
       <c r="E35" s="2"/>
@@ -4405,42 +4439,26 @@
       </c>
     </row>
     <row r="36" spans="1:36" x14ac:dyDescent="0.25">
-      <c r="A36" s="2" t="s">
-        <v>140</v>
-      </c>
-      <c r="B36" s="2" t="s">
-        <v>141</v>
-      </c>
-      <c r="C36" s="2" t="s">
-        <v>266</v>
-      </c>
-      <c r="D36" s="2" t="s">
-        <v>266</v>
-      </c>
-      <c r="E36" s="2" t="s">
-        <v>267</v>
-      </c>
+      <c r="A36" t="s">
+        <v>274</v>
+      </c>
+      <c r="B36" t="s">
+        <v>275</v>
+      </c>
+      <c r="C36" t="s">
+        <v>279</v>
+      </c>
+      <c r="D36" s="2"/>
+      <c r="E36" s="2"/>
       <c r="F36" s="2"/>
-      <c r="G36" s="2" t="s">
-        <v>107</v>
-      </c>
-      <c r="H36" s="2" t="s">
-        <v>108</v>
-      </c>
-      <c r="I36" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="J36" s="2" t="s">
-        <v>134</v>
-      </c>
+      <c r="G36" s="2"/>
+      <c r="H36" s="2"/>
+      <c r="I36" s="2"/>
+      <c r="J36" s="2"/>
       <c r="K36" s="2"/>
       <c r="L36" s="2"/>
-      <c r="M36" s="2" t="s">
-        <v>109</v>
-      </c>
-      <c r="N36" s="2" t="s">
-        <v>119</v>
-      </c>
+      <c r="M36" s="2"/>
+      <c r="N36" s="2"/>
       <c r="O36" s="2"/>
       <c r="P36" s="2"/>
       <c r="Q36" s="2"/>
@@ -4451,126 +4469,110 @@
       <c r="V36" s="2"/>
       <c r="W36" s="2"/>
       <c r="X36" s="2"/>
-      <c r="Y36" s="2" t="s">
-        <v>211</v>
-      </c>
-      <c r="Z36" s="2" t="s">
-        <v>112</v>
-      </c>
-      <c r="AA36" s="2" t="s">
-        <v>139</v>
-      </c>
-      <c r="AB36" s="2">
-        <v>8</v>
-      </c>
-      <c r="AC36" s="2" t="s">
-        <v>113</v>
-      </c>
-      <c r="AD36" s="2" t="s">
-        <v>114</v>
-      </c>
+      <c r="Y36" s="2"/>
+      <c r="Z36" s="2"/>
+      <c r="AA36" s="2"/>
+      <c r="AB36" s="2"/>
+      <c r="AC36" s="2"/>
+      <c r="AD36" s="2"/>
       <c r="AE36" s="2"/>
       <c r="AF36" s="2"/>
       <c r="AG36" s="2"/>
       <c r="AH36" s="2"/>
       <c r="AI36" s="2"/>
       <c r="AJ36">
-        <v>78</v>
+        <v>74</v>
       </c>
     </row>
-    <row r="37" spans="1:36" s="4" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A37" s="2" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>145</v>
+        <v>266</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>145</v>
+        <v>266</v>
       </c>
       <c r="E37" s="2" t="s">
-        <v>146</v>
+        <v>267</v>
       </c>
       <c r="F37" s="2"/>
       <c r="G37" s="2" t="s">
-        <v>147</v>
+        <v>107</v>
       </c>
       <c r="H37" s="2" t="s">
-        <v>148</v>
+        <v>108</v>
       </c>
       <c r="I37" s="2" t="s">
         <v>36</v>
       </c>
       <c r="J37" s="2" t="s">
-        <v>55</v>
+        <v>134</v>
       </c>
       <c r="K37" s="2"/>
       <c r="L37" s="2"/>
       <c r="M37" s="2" t="s">
-        <v>40</v>
+        <v>109</v>
       </c>
       <c r="N37" s="2" t="s">
-        <v>149</v>
-      </c>
-      <c r="O37" s="2" t="s">
-        <v>149</v>
-      </c>
-      <c r="P37" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="Q37" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="R37" s="2" t="s">
-        <v>150</v>
-      </c>
-      <c r="S37" s="2">
-        <v>1</v>
-      </c>
+        <v>119</v>
+      </c>
+      <c r="O37" s="2"/>
+      <c r="P37" s="2"/>
+      <c r="Q37" s="2"/>
+      <c r="R37" s="2"/>
+      <c r="S37" s="2"/>
       <c r="T37" s="2"/>
       <c r="U37" s="2"/>
       <c r="V37" s="2"/>
       <c r="W37" s="2"/>
       <c r="X37" s="2"/>
       <c r="Y37" s="2" t="s">
-        <v>111</v>
-      </c>
-      <c r="Z37" s="2"/>
-      <c r="AA37" s="2"/>
-      <c r="AB37" s="2"/>
-      <c r="AC37" s="2"/>
-      <c r="AD37" s="2"/>
-      <c r="AE37" s="2" t="s">
-        <v>151</v>
-      </c>
-      <c r="AF37" s="2" t="s">
-        <v>152</v>
-      </c>
+        <v>211</v>
+      </c>
+      <c r="Z37" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="AA37" s="2" t="s">
+        <v>139</v>
+      </c>
+      <c r="AB37" s="2">
+        <v>8</v>
+      </c>
+      <c r="AC37" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="AD37" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="AE37" s="2"/>
+      <c r="AF37" s="2"/>
       <c r="AG37" s="2"/>
       <c r="AH37" s="2"/>
       <c r="AI37" s="2"/>
-      <c r="AJ37" s="4">
-        <v>183</v>
+      <c r="AJ37">
+        <v>78</v>
       </c>
     </row>
     <row r="38" spans="1:36" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A38" s="2" t="s">
-        <v>153</v>
+        <v>143</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>154</v>
+        <v>144</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>155</v>
+        <v>145</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>155</v>
+        <v>145</v>
       </c>
       <c r="E38" s="2" t="s">
-        <v>156</v>
+        <v>146</v>
       </c>
       <c r="F38" s="2"/>
       <c r="G38" s="2" t="s">
@@ -4625,7 +4627,7 @@
         <v>151</v>
       </c>
       <c r="AF38" s="2" t="s">
-        <v>157</v>
+        <v>152</v>
       </c>
       <c r="AG38" s="2"/>
       <c r="AH38" s="2"/>
@@ -4636,19 +4638,19 @@
     </row>
     <row r="39" spans="1:36" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A39" s="2" t="s">
-        <v>158</v>
+        <v>153</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>159</v>
+        <v>154</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>160</v>
+        <v>155</v>
       </c>
       <c r="D39" s="2" t="s">
-        <v>160</v>
+        <v>155</v>
       </c>
       <c r="E39" s="2" t="s">
-        <v>161</v>
+        <v>156</v>
       </c>
       <c r="F39" s="2"/>
       <c r="G39" s="2" t="s">
@@ -4669,10 +4671,10 @@
         <v>40</v>
       </c>
       <c r="N39" s="2" t="s">
-        <v>162</v>
+        <v>149</v>
       </c>
       <c r="O39" s="2" t="s">
-        <v>162</v>
+        <v>149</v>
       </c>
       <c r="P39" s="2" t="s">
         <v>42</v>
@@ -4681,7 +4683,7 @@
         <v>43</v>
       </c>
       <c r="R39" s="2" t="s">
-        <v>163</v>
+        <v>150</v>
       </c>
       <c r="S39" s="2">
         <v>1</v>
@@ -4703,7 +4705,7 @@
         <v>151</v>
       </c>
       <c r="AF39" s="2" t="s">
-        <v>152</v>
+        <v>157</v>
       </c>
       <c r="AG39" s="2"/>
       <c r="AH39" s="2"/>
@@ -4714,19 +4716,19 @@
     </row>
     <row r="40" spans="1:36" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A40" s="2" t="s">
-        <v>164</v>
+        <v>158</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>165</v>
+        <v>159</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>166</v>
+        <v>160</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>166</v>
+        <v>160</v>
       </c>
       <c r="E40" s="2" t="s">
-        <v>167</v>
+        <v>161</v>
       </c>
       <c r="F40" s="2"/>
       <c r="G40" s="2" t="s">
@@ -4781,7 +4783,7 @@
         <v>151</v>
       </c>
       <c r="AF40" s="2" t="s">
-        <v>157</v>
+        <v>152</v>
       </c>
       <c r="AG40" s="2"/>
       <c r="AH40" s="2"/>
@@ -4792,19 +4794,19 @@
     </row>
     <row r="41" spans="1:36" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A41" s="2" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>169</v>
+        <v>165</v>
       </c>
       <c r="C41" s="2" t="s">
-        <v>170</v>
+        <v>166</v>
       </c>
       <c r="D41" s="2" t="s">
-        <v>170</v>
+        <v>166</v>
       </c>
       <c r="E41" s="2" t="s">
-        <v>171</v>
+        <v>167</v>
       </c>
       <c r="F41" s="2"/>
       <c r="G41" s="2" t="s">
@@ -4825,10 +4827,10 @@
         <v>40</v>
       </c>
       <c r="N41" s="2" t="s">
-        <v>172</v>
+        <v>162</v>
       </c>
       <c r="O41" s="2" t="s">
-        <v>172</v>
+        <v>162</v>
       </c>
       <c r="P41" s="2" t="s">
         <v>42</v>
@@ -4837,7 +4839,7 @@
         <v>43</v>
       </c>
       <c r="R41" s="2" t="s">
-        <v>173</v>
+        <v>163</v>
       </c>
       <c r="S41" s="2">
         <v>1</v>
@@ -4859,7 +4861,7 @@
         <v>151</v>
       </c>
       <c r="AF41" s="2" t="s">
-        <v>152</v>
+        <v>157</v>
       </c>
       <c r="AG41" s="2"/>
       <c r="AH41" s="2"/>
@@ -4870,19 +4872,19 @@
     </row>
     <row r="42" spans="1:36" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A42" s="2" t="s">
-        <v>174</v>
+        <v>168</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>175</v>
+        <v>169</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>176</v>
+        <v>170</v>
       </c>
       <c r="D42" s="2" t="s">
-        <v>176</v>
+        <v>170</v>
       </c>
       <c r="E42" s="2" t="s">
-        <v>177</v>
+        <v>171</v>
       </c>
       <c r="F42" s="2"/>
       <c r="G42" s="2" t="s">
@@ -4937,7 +4939,7 @@
         <v>151</v>
       </c>
       <c r="AF42" s="2" t="s">
-        <v>157</v>
+        <v>152</v>
       </c>
       <c r="AG42" s="2"/>
       <c r="AH42" s="2"/>
@@ -4948,19 +4950,19 @@
     </row>
     <row r="43" spans="1:36" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A43" s="2" t="s">
-        <v>178</v>
+        <v>174</v>
       </c>
       <c r="B43" s="2" t="s">
-        <v>179</v>
+        <v>175</v>
       </c>
       <c r="C43" s="2" t="s">
-        <v>180</v>
+        <v>176</v>
       </c>
       <c r="D43" s="2" t="s">
-        <v>180</v>
+        <v>176</v>
       </c>
       <c r="E43" s="2" t="s">
-        <v>181</v>
+        <v>177</v>
       </c>
       <c r="F43" s="2"/>
       <c r="G43" s="2" t="s">
@@ -4981,10 +4983,10 @@
         <v>40</v>
       </c>
       <c r="N43" s="2" t="s">
-        <v>149</v>
+        <v>172</v>
       </c>
       <c r="O43" s="2" t="s">
-        <v>149</v>
+        <v>172</v>
       </c>
       <c r="P43" s="2" t="s">
         <v>42</v>
@@ -4993,7 +4995,7 @@
         <v>43</v>
       </c>
       <c r="R43" s="2" t="s">
-        <v>150</v>
+        <v>173</v>
       </c>
       <c r="S43" s="2">
         <v>1</v>
@@ -5004,7 +5006,7 @@
       <c r="W43" s="2"/>
       <c r="X43" s="2"/>
       <c r="Y43" s="2" t="s">
-        <v>182</v>
+        <v>111</v>
       </c>
       <c r="Z43" s="2"/>
       <c r="AA43" s="2"/>
@@ -5015,30 +5017,30 @@
         <v>151</v>
       </c>
       <c r="AF43" s="2" t="s">
-        <v>152</v>
+        <v>157</v>
       </c>
       <c r="AG43" s="2"/>
       <c r="AH43" s="2"/>
       <c r="AI43" s="2"/>
       <c r="AJ43" s="4">
-        <v>184</v>
+        <v>183</v>
       </c>
     </row>
     <row r="44" spans="1:36" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A44" s="2" t="s">
-        <v>183</v>
+        <v>178</v>
       </c>
       <c r="B44" s="2" t="s">
-        <v>184</v>
+        <v>179</v>
       </c>
       <c r="C44" s="2" t="s">
-        <v>185</v>
+        <v>180</v>
       </c>
       <c r="D44" s="2" t="s">
-        <v>185</v>
+        <v>180</v>
       </c>
       <c r="E44" s="2" t="s">
-        <v>186</v>
+        <v>181</v>
       </c>
       <c r="F44" s="2"/>
       <c r="G44" s="2" t="s">
@@ -5093,7 +5095,7 @@
         <v>151</v>
       </c>
       <c r="AF44" s="2" t="s">
-        <v>157</v>
+        <v>152</v>
       </c>
       <c r="AG44" s="2"/>
       <c r="AH44" s="2"/>
@@ -5104,10 +5106,10 @@
     </row>
     <row r="45" spans="1:36" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A45" s="2" t="s">
-        <v>187</v>
+        <v>183</v>
       </c>
       <c r="B45" s="2" t="s">
-        <v>188</v>
+        <v>184</v>
       </c>
       <c r="C45" s="2" t="s">
         <v>185</v>
@@ -5182,19 +5184,19 @@
     </row>
     <row r="46" spans="1:36" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A46" s="2" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="B46" s="2" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="C46" s="2" t="s">
-        <v>191</v>
+        <v>185</v>
       </c>
       <c r="D46" s="2" t="s">
-        <v>191</v>
+        <v>185</v>
       </c>
       <c r="E46" s="2" t="s">
-        <v>192</v>
+        <v>186</v>
       </c>
       <c r="F46" s="2"/>
       <c r="G46" s="2" t="s">
@@ -5215,10 +5217,10 @@
         <v>40</v>
       </c>
       <c r="N46" s="2" t="s">
-        <v>162</v>
+        <v>149</v>
       </c>
       <c r="O46" s="2" t="s">
-        <v>162</v>
+        <v>149</v>
       </c>
       <c r="P46" s="2" t="s">
         <v>42</v>
@@ -5227,7 +5229,7 @@
         <v>43</v>
       </c>
       <c r="R46" s="2" t="s">
-        <v>163</v>
+        <v>150</v>
       </c>
       <c r="S46" s="2">
         <v>1</v>
@@ -5249,7 +5251,7 @@
         <v>151</v>
       </c>
       <c r="AF46" s="2" t="s">
-        <v>152</v>
+        <v>157</v>
       </c>
       <c r="AG46" s="2"/>
       <c r="AH46" s="2"/>
@@ -5260,19 +5262,19 @@
     </row>
     <row r="47" spans="1:36" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A47" s="2" t="s">
-        <v>193</v>
+        <v>189</v>
       </c>
       <c r="B47" s="2" t="s">
-        <v>194</v>
+        <v>190</v>
       </c>
       <c r="C47" s="2" t="s">
-        <v>195</v>
+        <v>191</v>
       </c>
       <c r="D47" s="2" t="s">
-        <v>195</v>
+        <v>191</v>
       </c>
       <c r="E47" s="2" t="s">
-        <v>196</v>
+        <v>192</v>
       </c>
       <c r="F47" s="2"/>
       <c r="G47" s="2" t="s">
@@ -5327,7 +5329,7 @@
         <v>151</v>
       </c>
       <c r="AF47" s="2" t="s">
-        <v>157</v>
+        <v>152</v>
       </c>
       <c r="AG47" s="2"/>
       <c r="AH47" s="2"/>
@@ -5338,10 +5340,10 @@
     </row>
     <row r="48" spans="1:36" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A48" s="2" t="s">
-        <v>197</v>
+        <v>193</v>
       </c>
       <c r="B48" s="2" t="s">
-        <v>198</v>
+        <v>194</v>
       </c>
       <c r="C48" s="2" t="s">
         <v>195</v>
@@ -5416,19 +5418,19 @@
     </row>
     <row r="49" spans="1:36" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A49" s="2" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="B49" s="2" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="C49" s="2" t="s">
-        <v>201</v>
+        <v>195</v>
       </c>
       <c r="D49" s="2" t="s">
-        <v>201</v>
+        <v>195</v>
       </c>
       <c r="E49" s="2" t="s">
-        <v>202</v>
+        <v>196</v>
       </c>
       <c r="F49" s="2"/>
       <c r="G49" s="2" t="s">
@@ -5449,10 +5451,10 @@
         <v>40</v>
       </c>
       <c r="N49" s="2" t="s">
-        <v>172</v>
+        <v>162</v>
       </c>
       <c r="O49" s="2" t="s">
-        <v>172</v>
+        <v>162</v>
       </c>
       <c r="P49" s="2" t="s">
         <v>42</v>
@@ -5461,7 +5463,7 @@
         <v>43</v>
       </c>
       <c r="R49" s="2" t="s">
-        <v>173</v>
+        <v>163</v>
       </c>
       <c r="S49" s="2">
         <v>1</v>
@@ -5483,7 +5485,7 @@
         <v>151</v>
       </c>
       <c r="AF49" s="2" t="s">
-        <v>152</v>
+        <v>157</v>
       </c>
       <c r="AG49" s="2"/>
       <c r="AH49" s="2"/>
@@ -5494,19 +5496,19 @@
     </row>
     <row r="50" spans="1:36" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A50" s="2" t="s">
-        <v>203</v>
+        <v>199</v>
       </c>
       <c r="B50" s="2" t="s">
-        <v>204</v>
+        <v>200</v>
       </c>
       <c r="C50" s="2" t="s">
-        <v>205</v>
+        <v>201</v>
       </c>
       <c r="D50" s="2" t="s">
-        <v>205</v>
+        <v>201</v>
       </c>
       <c r="E50" s="2" t="s">
-        <v>206</v>
+        <v>202</v>
       </c>
       <c r="F50" s="2"/>
       <c r="G50" s="2" t="s">
@@ -5561,7 +5563,7 @@
         <v>151</v>
       </c>
       <c r="AF50" s="2" t="s">
-        <v>157</v>
+        <v>152</v>
       </c>
       <c r="AG50" s="2"/>
       <c r="AH50" s="2"/>
@@ -5572,19 +5574,19 @@
     </row>
     <row r="51" spans="1:36" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A51" s="2" t="s">
-        <v>207</v>
+        <v>203</v>
       </c>
       <c r="B51" s="2" t="s">
-        <v>208</v>
+        <v>204</v>
       </c>
       <c r="C51" s="2" t="s">
-        <v>209</v>
+        <v>205</v>
       </c>
       <c r="D51" s="2" t="s">
-        <v>209</v>
+        <v>205</v>
       </c>
       <c r="E51" s="2" t="s">
-        <v>210</v>
+        <v>206</v>
       </c>
       <c r="F51" s="2"/>
       <c r="G51" s="2" t="s">
@@ -5605,10 +5607,10 @@
         <v>40</v>
       </c>
       <c r="N51" s="2" t="s">
-        <v>162</v>
+        <v>172</v>
       </c>
       <c r="O51" s="2" t="s">
-        <v>162</v>
+        <v>172</v>
       </c>
       <c r="P51" s="2" t="s">
         <v>42</v>
@@ -5617,7 +5619,7 @@
         <v>43</v>
       </c>
       <c r="R51" s="2" t="s">
-        <v>163</v>
+        <v>173</v>
       </c>
       <c r="S51" s="2">
         <v>1</v>
@@ -5628,7 +5630,7 @@
       <c r="W51" s="2"/>
       <c r="X51" s="2"/>
       <c r="Y51" s="2" t="s">
-        <v>211</v>
+        <v>182</v>
       </c>
       <c r="Z51" s="2"/>
       <c r="AA51" s="2"/>
@@ -5639,30 +5641,30 @@
         <v>151</v>
       </c>
       <c r="AF51" s="2" t="s">
-        <v>152</v>
+        <v>157</v>
       </c>
       <c r="AG51" s="2"/>
       <c r="AH51" s="2"/>
       <c r="AI51" s="2"/>
       <c r="AJ51" s="4">
-        <v>185</v>
+        <v>184</v>
       </c>
     </row>
     <row r="52" spans="1:36" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A52" s="2" t="s">
-        <v>212</v>
+        <v>207</v>
       </c>
       <c r="B52" s="2" t="s">
-        <v>213</v>
+        <v>208</v>
       </c>
       <c r="C52" s="2" t="s">
-        <v>214</v>
+        <v>209</v>
       </c>
       <c r="D52" s="2" t="s">
-        <v>214</v>
+        <v>209</v>
       </c>
       <c r="E52" s="2" t="s">
-        <v>215</v>
+        <v>210</v>
       </c>
       <c r="F52" s="2"/>
       <c r="G52" s="2" t="s">
@@ -5717,7 +5719,7 @@
         <v>151</v>
       </c>
       <c r="AF52" s="2" t="s">
-        <v>157</v>
+        <v>152</v>
       </c>
       <c r="AG52" s="2"/>
       <c r="AH52" s="2"/>
@@ -5728,19 +5730,19 @@
     </row>
     <row r="53" spans="1:36" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A53" s="2" t="s">
-        <v>216</v>
+        <v>212</v>
       </c>
       <c r="B53" s="2" t="s">
-        <v>217</v>
+        <v>213</v>
       </c>
       <c r="C53" s="2" t="s">
-        <v>218</v>
+        <v>214</v>
       </c>
       <c r="D53" s="2" t="s">
-        <v>218</v>
+        <v>214</v>
       </c>
       <c r="E53" s="2" t="s">
-        <v>219</v>
+        <v>215</v>
       </c>
       <c r="F53" s="2"/>
       <c r="G53" s="2" t="s">
@@ -5761,10 +5763,10 @@
         <v>40</v>
       </c>
       <c r="N53" s="2" t="s">
-        <v>172</v>
+        <v>162</v>
       </c>
       <c r="O53" s="2" t="s">
-        <v>172</v>
+        <v>162</v>
       </c>
       <c r="P53" s="2" t="s">
         <v>42</v>
@@ -5773,7 +5775,7 @@
         <v>43</v>
       </c>
       <c r="R53" s="2" t="s">
-        <v>173</v>
+        <v>163</v>
       </c>
       <c r="S53" s="2">
         <v>1</v>
@@ -5795,7 +5797,7 @@
         <v>151</v>
       </c>
       <c r="AF53" s="2" t="s">
-        <v>152</v>
+        <v>157</v>
       </c>
       <c r="AG53" s="2"/>
       <c r="AH53" s="2"/>
@@ -5806,19 +5808,19 @@
     </row>
     <row r="54" spans="1:36" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A54" s="2" t="s">
-        <v>220</v>
+        <v>216</v>
       </c>
       <c r="B54" s="2" t="s">
-        <v>221</v>
+        <v>217</v>
       </c>
       <c r="C54" s="2" t="s">
-        <v>222</v>
+        <v>218</v>
       </c>
       <c r="D54" s="2" t="s">
-        <v>222</v>
+        <v>218</v>
       </c>
       <c r="E54" s="2" t="s">
-        <v>223</v>
+        <v>219</v>
       </c>
       <c r="F54" s="2"/>
       <c r="G54" s="2" t="s">
@@ -5873,7 +5875,7 @@
         <v>151</v>
       </c>
       <c r="AF54" s="2" t="s">
-        <v>157</v>
+        <v>152</v>
       </c>
       <c r="AG54" s="2"/>
       <c r="AH54" s="2"/>
@@ -5884,10 +5886,10 @@
     </row>
     <row r="55" spans="1:36" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A55" s="2" t="s">
-        <v>224</v>
+        <v>220</v>
       </c>
       <c r="B55" s="2" t="s">
-        <v>225</v>
+        <v>221</v>
       </c>
       <c r="C55" s="2" t="s">
         <v>222</v>
@@ -5962,19 +5964,19 @@
     </row>
     <row r="56" spans="1:36" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A56" s="2" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="B56" s="2" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="C56" s="2" t="s">
-        <v>228</v>
+        <v>222</v>
       </c>
       <c r="D56" s="2" t="s">
-        <v>228</v>
+        <v>222</v>
       </c>
       <c r="E56" s="2" t="s">
-        <v>229</v>
+        <v>223</v>
       </c>
       <c r="F56" s="2"/>
       <c r="G56" s="2" t="s">
@@ -5995,10 +5997,10 @@
         <v>40</v>
       </c>
       <c r="N56" s="2" t="s">
-        <v>149</v>
+        <v>172</v>
       </c>
       <c r="O56" s="2" t="s">
-        <v>149</v>
+        <v>172</v>
       </c>
       <c r="P56" s="2" t="s">
         <v>42</v>
@@ -6007,7 +6009,7 @@
         <v>43</v>
       </c>
       <c r="R56" s="2" t="s">
-        <v>150</v>
+        <v>173</v>
       </c>
       <c r="S56" s="2">
         <v>1</v>
@@ -6029,7 +6031,7 @@
         <v>151</v>
       </c>
       <c r="AF56" s="2" t="s">
-        <v>152</v>
+        <v>157</v>
       </c>
       <c r="AG56" s="2"/>
       <c r="AH56" s="2"/>
@@ -6040,19 +6042,19 @@
     </row>
     <row r="57" spans="1:36" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A57" s="2" t="s">
-        <v>230</v>
+        <v>226</v>
       </c>
       <c r="B57" s="2" t="s">
-        <v>231</v>
+        <v>227</v>
       </c>
       <c r="C57" s="2" t="s">
-        <v>232</v>
+        <v>228</v>
       </c>
       <c r="D57" s="2" t="s">
-        <v>232</v>
+        <v>228</v>
       </c>
       <c r="E57" s="2" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
       <c r="F57" s="2"/>
       <c r="G57" s="2" t="s">
@@ -6107,7 +6109,7 @@
         <v>151</v>
       </c>
       <c r="AF57" s="2" t="s">
-        <v>157</v>
+        <v>152</v>
       </c>
       <c r="AG57" s="2"/>
       <c r="AH57" s="2"/>
@@ -6118,10 +6120,10 @@
     </row>
     <row r="58" spans="1:36" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A58" s="2" t="s">
-        <v>234</v>
+        <v>230</v>
       </c>
       <c r="B58" s="2" t="s">
-        <v>235</v>
+        <v>231</v>
       </c>
       <c r="C58" s="2" t="s">
         <v>232</v>
@@ -6196,83 +6198,97 @@
     </row>
     <row r="59" spans="1:36" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A59" s="2" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="B59" s="2" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="C59" s="2" t="s">
-        <v>238</v>
+        <v>232</v>
       </c>
       <c r="D59" s="2" t="s">
-        <v>238</v>
+        <v>232</v>
       </c>
       <c r="E59" s="2" t="s">
-        <v>239</v>
+        <v>233</v>
       </c>
       <c r="F59" s="2"/>
       <c r="G59" s="2" t="s">
-        <v>240</v>
+        <v>147</v>
       </c>
       <c r="H59" s="2" t="s">
-        <v>241</v>
+        <v>148</v>
       </c>
       <c r="I59" s="2" t="s">
-        <v>242</v>
-      </c>
-      <c r="J59" s="2"/>
+        <v>36</v>
+      </c>
+      <c r="J59" s="2" t="s">
+        <v>55</v>
+      </c>
       <c r="K59" s="2"/>
       <c r="L59" s="2"/>
-      <c r="M59" s="2"/>
-      <c r="N59" s="2"/>
-      <c r="O59" s="2"/>
-      <c r="P59" s="2"/>
-      <c r="Q59" s="2"/>
-      <c r="R59" s="2"/>
-      <c r="S59" s="2"/>
+      <c r="M59" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="N59" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="O59" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="P59" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="Q59" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="R59" s="2" t="s">
+        <v>150</v>
+      </c>
+      <c r="S59" s="2">
+        <v>1</v>
+      </c>
       <c r="T59" s="2"/>
       <c r="U59" s="2"/>
       <c r="V59" s="2"/>
       <c r="W59" s="2"/>
       <c r="X59" s="2"/>
-      <c r="Y59" s="2"/>
+      <c r="Y59" s="2" t="s">
+        <v>211</v>
+      </c>
       <c r="Z59" s="2"/>
       <c r="AA59" s="2"/>
       <c r="AB59" s="2"/>
       <c r="AC59" s="2"/>
       <c r="AD59" s="2"/>
-      <c r="AE59" s="2"/>
+      <c r="AE59" s="2" t="s">
+        <v>151</v>
+      </c>
       <c r="AF59" s="2" t="s">
         <v>157</v>
       </c>
-      <c r="AG59" s="2" t="s">
-        <v>139</v>
-      </c>
-      <c r="AH59" s="2" t="s">
-        <v>243</v>
-      </c>
-      <c r="AI59" s="2" t="s">
-        <v>244</v>
-      </c>
+      <c r="AG59" s="2"/>
+      <c r="AH59" s="2"/>
+      <c r="AI59" s="2"/>
       <c r="AJ59" s="4">
-        <v>186</v>
+        <v>185</v>
       </c>
     </row>
     <row r="60" spans="1:36" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A60" s="2" t="s">
-        <v>245</v>
+        <v>236</v>
       </c>
       <c r="B60" s="2" t="s">
-        <v>246</v>
+        <v>237</v>
       </c>
       <c r="C60" s="2" t="s">
-        <v>247</v>
+        <v>238</v>
       </c>
       <c r="D60" s="2" t="s">
-        <v>247</v>
+        <v>238</v>
       </c>
       <c r="E60" s="2" t="s">
-        <v>248</v>
+        <v>239</v>
       </c>
       <c r="F60" s="2"/>
       <c r="G60" s="2" t="s">
@@ -6316,7 +6332,7 @@
         <v>243</v>
       </c>
       <c r="AI60" s="2" t="s">
-        <v>249</v>
+        <v>244</v>
       </c>
       <c r="AJ60" s="4">
         <v>186</v>
@@ -6324,19 +6340,19 @@
     </row>
     <row r="61" spans="1:36" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A61" s="2" t="s">
-        <v>250</v>
+        <v>245</v>
       </c>
       <c r="B61" s="2" t="s">
-        <v>251</v>
+        <v>246</v>
       </c>
       <c r="C61" s="2" t="s">
-        <v>252</v>
+        <v>247</v>
       </c>
       <c r="D61" s="2" t="s">
-        <v>252</v>
+        <v>247</v>
       </c>
       <c r="E61" s="2" t="s">
-        <v>253</v>
+        <v>248</v>
       </c>
       <c r="F61" s="2"/>
       <c r="G61" s="2" t="s">
@@ -6380,14 +6396,78 @@
         <v>243</v>
       </c>
       <c r="AI61" s="2" t="s">
-        <v>254</v>
+        <v>249</v>
       </c>
       <c r="AJ61" s="4">
         <v>186</v>
       </c>
     </row>
+    <row r="62" spans="1:36" s="4" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A62" s="2" t="s">
+        <v>250</v>
+      </c>
+      <c r="B62" s="2" t="s">
+        <v>251</v>
+      </c>
+      <c r="C62" s="2" t="s">
+        <v>252</v>
+      </c>
+      <c r="D62" s="2" t="s">
+        <v>252</v>
+      </c>
+      <c r="E62" s="2" t="s">
+        <v>253</v>
+      </c>
+      <c r="F62" s="2"/>
+      <c r="G62" s="2" t="s">
+        <v>240</v>
+      </c>
+      <c r="H62" s="2" t="s">
+        <v>241</v>
+      </c>
+      <c r="I62" s="2" t="s">
+        <v>242</v>
+      </c>
+      <c r="J62" s="2"/>
+      <c r="K62" s="2"/>
+      <c r="L62" s="2"/>
+      <c r="M62" s="2"/>
+      <c r="N62" s="2"/>
+      <c r="O62" s="2"/>
+      <c r="P62" s="2"/>
+      <c r="Q62" s="2"/>
+      <c r="R62" s="2"/>
+      <c r="S62" s="2"/>
+      <c r="T62" s="2"/>
+      <c r="U62" s="2"/>
+      <c r="V62" s="2"/>
+      <c r="W62" s="2"/>
+      <c r="X62" s="2"/>
+      <c r="Y62" s="2"/>
+      <c r="Z62" s="2"/>
+      <c r="AA62" s="2"/>
+      <c r="AB62" s="2"/>
+      <c r="AC62" s="2"/>
+      <c r="AD62" s="2"/>
+      <c r="AE62" s="2"/>
+      <c r="AF62" s="2" t="s">
+        <v>157</v>
+      </c>
+      <c r="AG62" s="2" t="s">
+        <v>139</v>
+      </c>
+      <c r="AH62" s="2" t="s">
+        <v>243</v>
+      </c>
+      <c r="AI62" s="2" t="s">
+        <v>254</v>
+      </c>
+      <c r="AJ62" s="4">
+        <v>186</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:AJ61" xr:uid="{F51B6AD5-20E5-4E41-9D87-5C366E73940C}"/>
+  <autoFilter ref="A1:AJ62" xr:uid="{F51B6AD5-20E5-4E41-9D87-5C366E73940C}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
